--- a/data/split/test.xlsx
+++ b/data/split/test.xlsx
@@ -550,8 +550,10 @@
       <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="M2" t="n">
-        <v>4</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -617,8 +619,10 @@
       <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="M3" t="n">
-        <v>1</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -684,8 +688,10 @@
       <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="n">
-        <v>4</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N4" t="n">
         <v>1</v>
@@ -751,8 +757,10 @@
       <c r="L5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -818,8 +826,10 @@
       <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -885,8 +895,10 @@
       <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>5</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N7" t="n">
         <v>2</v>
@@ -952,8 +964,10 @@
       <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
-        <v>1</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -1019,8 +1033,10 @@
       <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>3</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1086,8 +1102,10 @@
       <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
-        <v>4</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1153,8 +1171,10 @@
       <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="n">
-        <v>1</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1358,8 +1378,10 @@
       <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="n">
-        <v>4</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N14" t="n">
         <v>2</v>
@@ -1563,8 +1585,10 @@
       <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="M17" t="n">
-        <v>4</v>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -1768,8 +1792,10 @@
       <c r="L20" t="n">
         <v>4</v>
       </c>
-      <c r="M20" t="n">
-        <v>1</v>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -1835,8 +1861,10 @@
       <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>4</v>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -1971,8 +1999,10 @@
       <c r="L23" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="n">
-        <v>4</v>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2038,8 +2068,10 @@
       <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="M24" t="n">
-        <v>4</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N24" t="n">
         <v>2</v>
@@ -2174,8 +2206,10 @@
       <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M26" t="n">
-        <v>4</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N26" t="n">
         <v>2</v>
@@ -2379,8 +2413,10 @@
       <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="M29" t="n">
-        <v>4</v>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N29" t="n">
         <v>2</v>
@@ -2446,8 +2482,10 @@
       <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="M30" t="n">
-        <v>4</v>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N30" t="n">
         <v>2</v>
@@ -2513,8 +2551,10 @@
       <c r="L31" t="n">
         <v>4</v>
       </c>
-      <c r="M31" t="n">
-        <v>4</v>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N31" t="n">
         <v>2</v>
@@ -2718,8 +2758,10 @@
       <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="n">
-        <v>4</v>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -2785,8 +2827,10 @@
       <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="M35" t="n">
-        <v>5</v>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N35" t="n">
         <v>2</v>
@@ -2852,8 +2896,10 @@
       <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="M36" t="n">
-        <v>4</v>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N36" t="n">
         <v>2</v>
@@ -2988,8 +3034,10 @@
       <c r="L38" t="n">
         <v>4</v>
       </c>
-      <c r="M38" t="n">
-        <v>3</v>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N38" t="n">
         <v>2</v>
@@ -3193,8 +3241,10 @@
       <c r="L41" t="n">
         <v>5</v>
       </c>
-      <c r="M41" t="n">
-        <v>1</v>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3329,8 +3379,10 @@
       <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="M43" t="n">
-        <v>4</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N43" t="n">
         <v>2</v>
@@ -3396,8 +3448,10 @@
       <c r="L44" t="n">
         <v>4</v>
       </c>
-      <c r="M44" t="n">
-        <v>4</v>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N44" t="n">
         <v>2</v>
@@ -3463,8 +3517,10 @@
       <c r="L45" t="n">
         <v>4</v>
       </c>
-      <c r="M45" t="n">
-        <v>4</v>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N45" t="n">
         <v>2</v>
@@ -3530,8 +3586,10 @@
       <c r="L46" t="n">
         <v>5</v>
       </c>
-      <c r="M46" t="n">
-        <v>4</v>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N46" t="n">
         <v>2</v>
@@ -3597,8 +3655,10 @@
       <c r="L47" t="n">
         <v>3</v>
       </c>
-      <c r="M47" t="n">
-        <v>4</v>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N47" t="n">
         <v>2</v>
@@ -3664,8 +3724,10 @@
       <c r="L48" t="n">
         <v>4</v>
       </c>
-      <c r="M48" t="n">
-        <v>4</v>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N48" t="n">
         <v>2</v>
@@ -3869,8 +3931,10 @@
       <c r="L51" t="n">
         <v>5</v>
       </c>
-      <c r="M51" t="n">
-        <v>1</v>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N51" t="n">
         <v>2</v>
@@ -3936,8 +4000,10 @@
       <c r="L52" t="n">
         <v>4</v>
       </c>
-      <c r="M52" t="n">
-        <v>4</v>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N52" t="n">
         <v>2</v>
@@ -4072,8 +4138,10 @@
       <c r="L54" t="n">
         <v>5</v>
       </c>
-      <c r="M54" t="n">
-        <v>2</v>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N54" t="n">
         <v>2</v>
@@ -4208,8 +4276,10 @@
       <c r="L56" t="n">
         <v>4</v>
       </c>
-      <c r="M56" t="n">
-        <v>4</v>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N56" t="n">
         <v>2</v>
@@ -4275,8 +4345,10 @@
       <c r="L57" t="n">
         <v>4</v>
       </c>
-      <c r="M57" t="n">
-        <v>1</v>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N57" t="n">
         <v>1</v>
@@ -4342,8 +4414,10 @@
       <c r="L58" t="n">
         <v>5</v>
       </c>
-      <c r="M58" t="n">
-        <v>1</v>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N58" t="n">
         <v>1</v>
@@ -4409,8 +4483,10 @@
       <c r="L59" t="n">
         <v>3</v>
       </c>
-      <c r="M59" t="n">
-        <v>5</v>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N59" t="n">
         <v>1</v>
@@ -4545,8 +4621,10 @@
       <c r="L61" t="n">
         <v>5</v>
       </c>
-      <c r="M61" t="n">
-        <v>1</v>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N61" t="n">
         <v>1</v>
@@ -4681,8 +4759,10 @@
       <c r="L63" t="n">
         <v>4</v>
       </c>
-      <c r="M63" t="n">
-        <v>5</v>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N63" t="n">
         <v>2</v>
@@ -4748,8 +4828,10 @@
       <c r="L64" t="n">
         <v>2</v>
       </c>
-      <c r="M64" t="n">
-        <v>5</v>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N64" t="n">
         <v>2</v>
@@ -4815,8 +4897,10 @@
       <c r="L65" t="n">
         <v>4</v>
       </c>
-      <c r="M65" t="n">
-        <v>5</v>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N65" t="n">
         <v>2</v>
@@ -4951,8 +5035,10 @@
       <c r="L67" t="n">
         <v>4</v>
       </c>
-      <c r="M67" t="n">
-        <v>5</v>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N67" t="n">
         <v>2</v>
@@ -5018,8 +5104,10 @@
       <c r="L68" t="n">
         <v>2</v>
       </c>
-      <c r="M68" t="n">
-        <v>4</v>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N68" t="n">
         <v>3</v>
@@ -5085,8 +5173,10 @@
       <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="n">
-        <v>5</v>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N69" t="n">
         <v>3</v>
@@ -5152,8 +5242,10 @@
       <c r="L70" t="n">
         <v>4</v>
       </c>
-      <c r="M70" t="n">
-        <v>4</v>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N70" t="n">
         <v>2</v>
@@ -5219,8 +5311,10 @@
       <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="M71" t="n">
-        <v>4</v>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N71" t="n">
         <v>2</v>
@@ -5286,8 +5380,10 @@
       <c r="L72" t="n">
         <v>5</v>
       </c>
-      <c r="M72" t="n">
-        <v>1</v>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N72" t="n">
         <v>2</v>
@@ -5422,8 +5518,10 @@
       <c r="L74" t="n">
         <v>2</v>
       </c>
-      <c r="M74" t="n">
-        <v>3</v>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N74" t="n">
         <v>2</v>
@@ -5489,8 +5587,10 @@
       <c r="L75" t="n">
         <v>4</v>
       </c>
-      <c r="M75" t="n">
-        <v>2</v>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N75" t="n">
         <v>1</v>
@@ -5694,8 +5794,10 @@
       <c r="L78" t="n">
         <v>2</v>
       </c>
-      <c r="M78" t="n">
-        <v>4</v>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N78" t="n">
         <v>2</v>
@@ -5761,8 +5863,10 @@
       <c r="L79" t="n">
         <v>4</v>
       </c>
-      <c r="M79" t="n">
-        <v>4</v>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N79" t="n">
         <v>2</v>
@@ -5828,8 +5932,10 @@
       <c r="L80" t="n">
         <v>4</v>
       </c>
-      <c r="M80" t="n">
-        <v>5</v>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N80" t="n">
         <v>2</v>
@@ -5895,8 +6001,10 @@
       <c r="L81" t="n">
         <v>2</v>
       </c>
-      <c r="M81" t="n">
-        <v>4</v>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N81" t="n">
         <v>2</v>
@@ -5962,8 +6070,10 @@
       <c r="L82" t="n">
         <v>5</v>
       </c>
-      <c r="M82" t="n">
-        <v>4</v>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N82" t="n">
         <v>2</v>
@@ -6029,8 +6139,10 @@
       <c r="L83" t="n">
         <v>4</v>
       </c>
-      <c r="M83" t="n">
-        <v>1</v>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N83" t="n">
         <v>1</v>
@@ -6096,8 +6208,10 @@
       <c r="L84" t="n">
         <v>4</v>
       </c>
-      <c r="M84" t="n">
-        <v>4</v>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N84" t="n">
         <v>1</v>
@@ -6232,8 +6346,10 @@
       <c r="L86" t="n">
         <v>2</v>
       </c>
-      <c r="M86" t="n">
-        <v>4</v>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N86" t="n">
         <v>2</v>
@@ -6299,8 +6415,10 @@
       <c r="L87" t="n">
         <v>2</v>
       </c>
-      <c r="M87" t="n">
-        <v>4</v>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N87" t="n">
         <v>3</v>
@@ -6366,8 +6484,10 @@
       <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="M88" t="n">
-        <v>4</v>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N88" t="n">
         <v>2</v>
@@ -6502,8 +6622,10 @@
       <c r="L90" t="n">
         <v>4</v>
       </c>
-      <c r="M90" t="n">
-        <v>4</v>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N90" t="n">
         <v>2</v>
@@ -6569,8 +6691,10 @@
       <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="M91" t="n">
-        <v>4</v>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N91" t="n">
         <v>2</v>
@@ -6774,8 +6898,10 @@
       <c r="L94" t="n">
         <v>4</v>
       </c>
-      <c r="M94" t="n">
-        <v>4</v>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N94" t="n">
         <v>2</v>
@@ -6841,8 +6967,10 @@
       <c r="L95" t="n">
         <v>5</v>
       </c>
-      <c r="M95" t="n">
-        <v>4</v>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N95" t="n">
         <v>2</v>
@@ -6908,8 +7036,10 @@
       <c r="L96" t="n">
         <v>3</v>
       </c>
-      <c r="M96" t="n">
-        <v>5</v>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N96" t="n">
         <v>2</v>
@@ -7044,8 +7174,10 @@
       <c r="L98" t="n">
         <v>4</v>
       </c>
-      <c r="M98" t="n">
-        <v>4</v>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N98" t="n">
         <v>2</v>
@@ -7111,8 +7243,10 @@
       <c r="L99" t="n">
         <v>5</v>
       </c>
-      <c r="M99" t="n">
-        <v>5</v>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N99" t="n">
         <v>2</v>
@@ -7178,8 +7312,10 @@
       <c r="L100" t="n">
         <v>4</v>
       </c>
-      <c r="M100" t="n">
-        <v>5</v>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N100" t="n">
         <v>2</v>
@@ -7245,8 +7381,10 @@
       <c r="L101" t="n">
         <v>5</v>
       </c>
-      <c r="M101" t="n">
-        <v>3</v>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N101" t="n">
         <v>2</v>
@@ -7450,8 +7588,10 @@
       <c r="L104" t="n">
         <v>5</v>
       </c>
-      <c r="M104" t="n">
-        <v>5</v>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N104" t="n">
         <v>2</v>
@@ -7517,8 +7657,10 @@
       <c r="L105" t="n">
         <v>4</v>
       </c>
-      <c r="M105" t="n">
-        <v>4</v>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N105" t="n">
         <v>2</v>
@@ -7584,8 +7726,10 @@
       <c r="L106" t="n">
         <v>4</v>
       </c>
-      <c r="M106" t="n">
-        <v>4</v>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N106" t="n">
         <v>2</v>
@@ -7651,8 +7795,10 @@
       <c r="L107" t="n">
         <v>4</v>
       </c>
-      <c r="M107" t="n">
-        <v>4</v>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N107" t="n">
         <v>2</v>
@@ -7718,8 +7864,10 @@
       <c r="L108" t="n">
         <v>4</v>
       </c>
-      <c r="M108" t="n">
-        <v>4</v>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N108" t="n">
         <v>2</v>
@@ -7785,8 +7933,10 @@
       <c r="L109" t="n">
         <v>2</v>
       </c>
-      <c r="M109" t="n">
-        <v>4</v>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N109" t="n">
         <v>2</v>
@@ -7921,8 +8071,10 @@
       <c r="L111" t="n">
         <v>5</v>
       </c>
-      <c r="M111" t="n">
-        <v>4</v>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N111" t="n">
         <v>2</v>
@@ -8057,8 +8209,10 @@
       <c r="L113" t="n">
         <v>4</v>
       </c>
-      <c r="M113" t="n">
-        <v>4</v>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N113" t="n">
         <v>2</v>
@@ -8124,8 +8278,10 @@
       <c r="L114" t="n">
         <v>3</v>
       </c>
-      <c r="M114" t="n">
-        <v>4</v>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N114" t="n">
         <v>2</v>
@@ -8191,8 +8347,10 @@
       <c r="L115" t="n">
         <v>2</v>
       </c>
-      <c r="M115" t="n">
-        <v>5</v>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N115" t="n">
         <v>2</v>
@@ -8258,8 +8416,10 @@
       <c r="L116" t="n">
         <v>1</v>
       </c>
-      <c r="M116" t="n">
-        <v>5</v>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N116" t="n">
         <v>2</v>
@@ -8394,8 +8554,10 @@
       <c r="L118" t="n">
         <v>5</v>
       </c>
-      <c r="M118" t="n">
-        <v>4</v>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N118" t="n">
         <v>2</v>
@@ -8461,8 +8623,10 @@
       <c r="L119" t="n">
         <v>2</v>
       </c>
-      <c r="M119" t="n">
-        <v>4</v>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N119" t="n">
         <v>2</v>
@@ -8597,8 +8761,10 @@
       <c r="L121" t="n">
         <v>5</v>
       </c>
-      <c r="M121" t="n">
-        <v>4</v>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N121" t="n">
         <v>2</v>
@@ -8664,8 +8830,10 @@
       <c r="L122" t="n">
         <v>4</v>
       </c>
-      <c r="M122" t="n">
-        <v>5</v>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N122" t="n">
         <v>1</v>
@@ -8731,8 +8899,10 @@
       <c r="L123" t="n">
         <v>3</v>
       </c>
-      <c r="M123" t="n">
-        <v>4</v>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N123" t="n">
         <v>2</v>
@@ -8936,8 +9106,10 @@
       <c r="L126" t="n">
         <v>5</v>
       </c>
-      <c r="M126" t="n">
-        <v>4</v>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N126" t="n">
         <v>2</v>
@@ -9003,8 +9175,10 @@
       <c r="L127" t="n">
         <v>3</v>
       </c>
-      <c r="M127" t="n">
-        <v>1</v>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N127" t="n">
         <v>0</v>
@@ -9139,8 +9313,10 @@
       <c r="L129" t="n">
         <v>2</v>
       </c>
-      <c r="M129" t="n">
-        <v>4</v>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N129" t="n">
         <v>2</v>
@@ -9206,8 +9382,10 @@
       <c r="L130" t="n">
         <v>5</v>
       </c>
-      <c r="M130" t="n">
-        <v>4</v>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N130" t="n">
         <v>2</v>
@@ -9342,8 +9520,10 @@
       <c r="L132" t="n">
         <v>4</v>
       </c>
-      <c r="M132" t="n">
-        <v>4</v>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N132" t="n">
         <v>2</v>
@@ -9409,8 +9589,10 @@
       <c r="L133" t="n">
         <v>5</v>
       </c>
-      <c r="M133" t="n">
-        <v>1</v>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N133" t="n">
         <v>2</v>
@@ -9614,8 +9796,10 @@
       <c r="L136" t="n">
         <v>3</v>
       </c>
-      <c r="M136" t="n">
-        <v>1</v>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N136" t="n">
         <v>2</v>
@@ -9681,8 +9865,10 @@
       <c r="L137" t="n">
         <v>4</v>
       </c>
-      <c r="M137" t="n">
-        <v>4</v>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N137" t="n">
         <v>2</v>
@@ -9748,8 +9934,10 @@
       <c r="L138" t="n">
         <v>4</v>
       </c>
-      <c r="M138" t="n">
-        <v>3</v>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N138" t="n">
         <v>2</v>
@@ -9815,8 +10003,10 @@
       <c r="L139" t="n">
         <v>2</v>
       </c>
-      <c r="M139" t="n">
-        <v>4</v>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N139" t="n">
         <v>2</v>
@@ -9951,8 +10141,10 @@
       <c r="L141" t="n">
         <v>5</v>
       </c>
-      <c r="M141" t="n">
-        <v>4</v>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N141" t="n">
         <v>1</v>
@@ -10018,8 +10210,10 @@
       <c r="L142" t="n">
         <v>5</v>
       </c>
-      <c r="M142" t="n">
-        <v>4</v>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N142" t="n">
         <v>2</v>
@@ -10085,8 +10279,10 @@
       <c r="L143" t="n">
         <v>4</v>
       </c>
-      <c r="M143" t="n">
-        <v>1</v>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N143" t="n">
         <v>0</v>
@@ -10359,8 +10555,10 @@
       <c r="L147" t="n">
         <v>5</v>
       </c>
-      <c r="M147" t="n">
-        <v>4</v>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N147" t="n">
         <v>1</v>
@@ -10426,8 +10624,10 @@
       <c r="L148" t="n">
         <v>4</v>
       </c>
-      <c r="M148" t="n">
-        <v>1</v>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N148" t="n">
         <v>2</v>
@@ -10562,8 +10762,10 @@
       <c r="L150" t="n">
         <v>3</v>
       </c>
-      <c r="M150" t="n">
-        <v>3</v>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N150" t="n">
         <v>2</v>
@@ -10629,8 +10831,10 @@
       <c r="L151" t="n">
         <v>5</v>
       </c>
-      <c r="M151" t="n">
-        <v>4</v>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N151" t="n">
         <v>1</v>
@@ -10834,8 +11038,10 @@
       <c r="L154" t="n">
         <v>4</v>
       </c>
-      <c r="M154" t="n">
-        <v>4</v>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N154" t="n">
         <v>2</v>
@@ -10901,8 +11107,10 @@
       <c r="L155" t="n">
         <v>4</v>
       </c>
-      <c r="M155" t="n">
-        <v>2</v>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N155" t="n">
         <v>2</v>
@@ -11037,8 +11245,10 @@
       <c r="L157" t="n">
         <v>5</v>
       </c>
-      <c r="M157" t="n">
-        <v>4</v>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N157" t="n">
         <v>2</v>
@@ -11104,8 +11314,10 @@
       <c r="L158" t="n">
         <v>4</v>
       </c>
-      <c r="M158" t="n">
-        <v>5</v>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N158" t="n">
         <v>2</v>
@@ -11171,8 +11383,10 @@
       <c r="L159" t="n">
         <v>3</v>
       </c>
-      <c r="M159" t="n">
-        <v>4</v>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N159" t="n">
         <v>2</v>
@@ -11376,8 +11590,10 @@
       <c r="L162" t="n">
         <v>5</v>
       </c>
-      <c r="M162" t="n">
-        <v>1</v>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N162" t="n">
         <v>1</v>
@@ -11443,8 +11659,10 @@
       <c r="L163" t="n">
         <v>4</v>
       </c>
-      <c r="M163" t="n">
-        <v>4</v>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N163" t="n">
         <v>2</v>
@@ -11510,8 +11728,10 @@
       <c r="L164" t="n">
         <v>4</v>
       </c>
-      <c r="M164" t="n">
-        <v>4</v>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N164" t="n">
         <v>2</v>
@@ -11577,8 +11797,10 @@
       <c r="L165" t="n">
         <v>2</v>
       </c>
-      <c r="M165" t="n">
-        <v>4</v>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N165" t="n">
         <v>2</v>
@@ -11644,8 +11866,10 @@
       <c r="L166" t="n">
         <v>5</v>
       </c>
-      <c r="M166" t="n">
-        <v>4</v>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N166" t="n">
         <v>1</v>
@@ -11711,8 +11935,10 @@
       <c r="L167" t="n">
         <v>2</v>
       </c>
-      <c r="M167" t="n">
-        <v>4</v>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N167" t="n">
         <v>0</v>
@@ -11778,8 +12004,10 @@
       <c r="L168" t="n">
         <v>5</v>
       </c>
-      <c r="M168" t="n">
-        <v>1</v>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N168" t="n">
         <v>2</v>
@@ -11914,8 +12142,10 @@
       <c r="L170" t="n">
         <v>4</v>
       </c>
-      <c r="M170" t="n">
-        <v>4</v>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N170" t="n">
         <v>2</v>
@@ -11981,8 +12211,10 @@
       <c r="L171" t="n">
         <v>4</v>
       </c>
-      <c r="M171" t="n">
-        <v>4</v>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N171" t="n">
         <v>2</v>
@@ -12048,8 +12280,10 @@
       <c r="L172" t="n">
         <v>4</v>
       </c>
-      <c r="M172" t="n">
-        <v>4</v>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N172" t="n">
         <v>0</v>
@@ -12184,8 +12418,10 @@
       <c r="L174" t="n">
         <v>4</v>
       </c>
-      <c r="M174" t="n">
-        <v>4</v>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N174" t="n">
         <v>2</v>
@@ -12458,8 +12694,10 @@
       <c r="L178" t="n">
         <v>2</v>
       </c>
-      <c r="M178" t="n">
-        <v>5</v>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N178" t="n">
         <v>2</v>
@@ -12525,8 +12763,10 @@
       <c r="L179" t="n">
         <v>4</v>
       </c>
-      <c r="M179" t="n">
-        <v>4</v>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N179" t="n">
         <v>2</v>
@@ -12661,8 +12901,10 @@
       <c r="L181" t="n">
         <v>4</v>
       </c>
-      <c r="M181" t="n">
-        <v>5</v>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N181" t="n">
         <v>2</v>
@@ -12728,8 +12970,10 @@
       <c r="L182" t="n">
         <v>5</v>
       </c>
-      <c r="M182" t="n">
-        <v>5</v>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N182" t="n">
         <v>2</v>
@@ -12795,8 +13039,10 @@
       <c r="L183" t="n">
         <v>3</v>
       </c>
-      <c r="M183" t="n">
-        <v>4</v>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N183" t="n">
         <v>2</v>
@@ -12862,8 +13108,10 @@
       <c r="L184" t="n">
         <v>4</v>
       </c>
-      <c r="M184" t="n">
-        <v>5</v>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N184" t="n">
         <v>1</v>
@@ -13136,8 +13384,10 @@
       <c r="L188" t="n">
         <v>2</v>
       </c>
-      <c r="M188" t="n">
-        <v>4</v>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N188" t="n">
         <v>3</v>
@@ -13272,8 +13522,10 @@
       <c r="L190" t="n">
         <v>2</v>
       </c>
-      <c r="M190" t="n">
-        <v>4</v>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N190" t="n">
         <v>3</v>
@@ -13339,8 +13591,10 @@
       <c r="L191" t="n">
         <v>3</v>
       </c>
-      <c r="M191" t="n">
-        <v>4</v>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N191" t="n">
         <v>2</v>
@@ -13406,8 +13660,10 @@
       <c r="L192" t="n">
         <v>5</v>
       </c>
-      <c r="M192" t="n">
-        <v>1</v>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N192" t="n">
         <v>2</v>
@@ -13473,8 +13729,10 @@
       <c r="L193" t="n">
         <v>4</v>
       </c>
-      <c r="M193" t="n">
-        <v>4</v>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N193" t="n">
         <v>2</v>
@@ -13609,8 +13867,10 @@
       <c r="L195" t="n">
         <v>3</v>
       </c>
-      <c r="M195" t="n">
-        <v>4</v>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N195" t="n">
         <v>2</v>
@@ -13676,8 +13936,10 @@
       <c r="L196" t="n">
         <v>5</v>
       </c>
-      <c r="M196" t="n">
-        <v>4</v>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N196" t="n">
         <v>2</v>
@@ -13812,8 +14074,10 @@
       <c r="L198" t="n">
         <v>2</v>
       </c>
-      <c r="M198" t="n">
-        <v>4</v>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N198" t="n">
         <v>2</v>
@@ -13948,8 +14212,10 @@
       <c r="L200" t="n">
         <v>4</v>
       </c>
-      <c r="M200" t="n">
-        <v>4</v>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N200" t="n">
         <v>2</v>
@@ -14015,8 +14281,10 @@
       <c r="L201" t="n">
         <v>4</v>
       </c>
-      <c r="M201" t="n">
-        <v>4</v>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N201" t="n">
         <v>2</v>
@@ -14082,8 +14350,10 @@
       <c r="L202" t="n">
         <v>2</v>
       </c>
-      <c r="M202" t="n">
-        <v>4</v>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N202" t="n">
         <v>1</v>
@@ -14149,8 +14419,10 @@
       <c r="L203" t="n">
         <v>5</v>
       </c>
-      <c r="M203" t="n">
-        <v>1</v>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N203" t="n">
         <v>1</v>
@@ -14285,8 +14557,10 @@
       <c r="L205" t="n">
         <v>3</v>
       </c>
-      <c r="M205" t="n">
-        <v>4</v>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N205" t="n">
         <v>2</v>
@@ -14421,8 +14695,10 @@
       <c r="L207" t="n">
         <v>4</v>
       </c>
-      <c r="M207" t="n">
-        <v>4</v>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N207" t="n">
         <v>2</v>
@@ -14557,8 +14833,10 @@
       <c r="L209" t="n">
         <v>2</v>
       </c>
-      <c r="M209" t="n">
-        <v>4</v>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N209" t="n">
         <v>3</v>
@@ -14693,8 +14971,10 @@
       <c r="L211" t="n">
         <v>4</v>
       </c>
-      <c r="M211" t="n">
-        <v>4</v>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N211" t="n">
         <v>2</v>
@@ -14760,8 +15040,10 @@
       <c r="L212" t="n">
         <v>2</v>
       </c>
-      <c r="M212" t="n">
-        <v>4</v>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N212" t="n">
         <v>2</v>
@@ -14827,8 +15109,10 @@
       <c r="L213" t="n">
         <v>4</v>
       </c>
-      <c r="M213" t="n">
-        <v>4</v>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N213" t="n">
         <v>2</v>
@@ -14894,8 +15178,10 @@
       <c r="L214" t="n">
         <v>4</v>
       </c>
-      <c r="M214" t="n">
-        <v>5</v>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N214" t="n">
         <v>2</v>
@@ -15099,8 +15385,10 @@
       <c r="L217" t="n">
         <v>5</v>
       </c>
-      <c r="M217" t="n">
-        <v>4</v>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N217" t="n">
         <v>2</v>
@@ -15235,8 +15523,10 @@
       <c r="L219" t="n">
         <v>5</v>
       </c>
-      <c r="M219" t="n">
-        <v>5</v>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N219" t="n">
         <v>2</v>
@@ -15302,8 +15592,10 @@
       <c r="L220" t="n">
         <v>5</v>
       </c>
-      <c r="M220" t="n">
-        <v>4</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N220" t="n">
         <v>2</v>
@@ -15438,8 +15730,10 @@
       <c r="L222" t="n">
         <v>2</v>
       </c>
-      <c r="M222" t="n">
-        <v>4</v>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N222" t="n">
         <v>3</v>
@@ -15574,8 +15868,10 @@
       <c r="L224" t="n">
         <v>3</v>
       </c>
-      <c r="M224" t="n">
-        <v>5</v>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N224" t="n">
         <v>2</v>
@@ -15641,8 +15937,10 @@
       <c r="L225" t="n">
         <v>4</v>
       </c>
-      <c r="M225" t="n">
-        <v>4</v>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N225" t="n">
         <v>2</v>
@@ -15777,8 +16075,10 @@
       <c r="L227" t="n">
         <v>4</v>
       </c>
-      <c r="M227" t="n">
-        <v>4</v>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N227" t="n">
         <v>2</v>
@@ -15844,8 +16144,10 @@
       <c r="L228" t="n">
         <v>4</v>
       </c>
-      <c r="M228" t="n">
-        <v>4</v>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N228" t="n">
         <v>2</v>
@@ -15911,8 +16213,10 @@
       <c r="L229" t="n">
         <v>3</v>
       </c>
-      <c r="M229" t="n">
-        <v>5</v>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N229" t="n">
         <v>2</v>
@@ -16185,8 +16489,10 @@
       <c r="L233" t="n">
         <v>2</v>
       </c>
-      <c r="M233" t="n">
-        <v>4</v>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N233" t="n">
         <v>2</v>
@@ -16528,8 +16834,10 @@
       <c r="L238" t="n">
         <v>4</v>
       </c>
-      <c r="M238" t="n">
-        <v>4</v>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N238" t="n">
         <v>2</v>
@@ -16595,8 +16903,10 @@
       <c r="L239" t="n">
         <v>5</v>
       </c>
-      <c r="M239" t="n">
-        <v>4</v>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N239" t="n">
         <v>2</v>
@@ -16731,8 +17041,10 @@
       <c r="L241" t="n">
         <v>4</v>
       </c>
-      <c r="M241" t="n">
-        <v>4</v>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N241" t="n">
         <v>2</v>
@@ -16798,8 +17110,10 @@
       <c r="L242" t="n">
         <v>4</v>
       </c>
-      <c r="M242" t="n">
-        <v>4</v>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N242" t="n">
         <v>1</v>
@@ -16865,8 +17179,10 @@
       <c r="L243" t="n">
         <v>4</v>
       </c>
-      <c r="M243" t="n">
-        <v>3</v>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N243" t="n">
         <v>0</v>
@@ -16932,8 +17248,10 @@
       <c r="L244" t="n">
         <v>4</v>
       </c>
-      <c r="M244" t="n">
-        <v>1</v>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N244" t="n">
         <v>1</v>
@@ -17068,8 +17386,10 @@
       <c r="L246" t="n">
         <v>4</v>
       </c>
-      <c r="M246" t="n">
-        <v>4</v>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N246" t="n">
         <v>2</v>
@@ -17135,8 +17455,10 @@
       <c r="L247" t="n">
         <v>3</v>
       </c>
-      <c r="M247" t="n">
-        <v>5</v>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N247" t="n">
         <v>2</v>
@@ -17202,8 +17524,10 @@
       <c r="L248" t="n">
         <v>2</v>
       </c>
-      <c r="M248" t="n">
-        <v>4</v>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N248" t="n">
         <v>2</v>
@@ -17407,8 +17731,10 @@
       <c r="L251" t="n">
         <v>4</v>
       </c>
-      <c r="M251" t="n">
-        <v>4</v>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N251" t="n">
         <v>2</v>
@@ -17474,8 +17800,10 @@
       <c r="L252" t="n">
         <v>4</v>
       </c>
-      <c r="M252" t="n">
-        <v>4</v>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N252" t="n">
         <v>2</v>
@@ -17541,8 +17869,10 @@
       <c r="L253" t="n">
         <v>4</v>
       </c>
-      <c r="M253" t="n">
-        <v>4</v>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N253" t="n">
         <v>1</v>
@@ -17815,8 +18145,10 @@
       <c r="L257" t="n">
         <v>4</v>
       </c>
-      <c r="M257" t="n">
-        <v>5</v>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N257" t="n">
         <v>1</v>
@@ -17882,8 +18214,10 @@
       <c r="L258" t="n">
         <v>4</v>
       </c>
-      <c r="M258" t="n">
-        <v>5</v>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N258" t="n">
         <v>2</v>
@@ -17949,8 +18283,10 @@
       <c r="L259" t="n">
         <v>5</v>
       </c>
-      <c r="M259" t="n">
-        <v>4</v>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N259" t="n">
         <v>0</v>
@@ -18016,8 +18352,10 @@
       <c r="L260" t="n">
         <v>2</v>
       </c>
-      <c r="M260" t="n">
-        <v>4</v>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N260" t="n">
         <v>2</v>
@@ -18083,8 +18421,10 @@
       <c r="L261" t="n">
         <v>5</v>
       </c>
-      <c r="M261" t="n">
-        <v>1</v>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N261" t="n">
         <v>2</v>
@@ -18150,8 +18490,10 @@
       <c r="L262" t="n">
         <v>4</v>
       </c>
-      <c r="M262" t="n">
-        <v>1</v>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N262" t="n">
         <v>2</v>
@@ -18217,8 +18559,10 @@
       <c r="L263" t="n">
         <v>5</v>
       </c>
-      <c r="M263" t="n">
-        <v>1</v>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N263" t="n">
         <v>2</v>
@@ -18284,8 +18628,10 @@
       <c r="L264" t="n">
         <v>4</v>
       </c>
-      <c r="M264" t="n">
-        <v>4</v>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N264" t="n">
         <v>2</v>
@@ -18420,8 +18766,10 @@
       <c r="L266" t="n">
         <v>5</v>
       </c>
-      <c r="M266" t="n">
-        <v>5</v>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N266" t="n">
         <v>2</v>
@@ -18487,8 +18835,10 @@
       <c r="L267" t="n">
         <v>3</v>
       </c>
-      <c r="M267" t="n">
-        <v>4</v>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N267" t="n">
         <v>2</v>
@@ -18554,8 +18904,10 @@
       <c r="L268" t="n">
         <v>4</v>
       </c>
-      <c r="M268" t="n">
-        <v>2</v>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N268" t="n">
         <v>2</v>
@@ -18621,8 +18973,10 @@
       <c r="L269" t="n">
         <v>4</v>
       </c>
-      <c r="M269" t="n">
-        <v>5</v>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N269" t="n">
         <v>2</v>
@@ -18757,8 +19111,10 @@
       <c r="L271" t="n">
         <v>5</v>
       </c>
-      <c r="M271" t="n">
-        <v>4</v>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N271" t="n">
         <v>2</v>
@@ -18824,8 +19180,10 @@
       <c r="L272" t="n">
         <v>5</v>
       </c>
-      <c r="M272" t="n">
-        <v>5</v>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N272" t="n">
         <v>2</v>
@@ -18891,8 +19249,10 @@
       <c r="L273" t="n">
         <v>4</v>
       </c>
-      <c r="M273" t="n">
-        <v>4</v>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N273" t="n">
         <v>2</v>
@@ -19027,8 +19387,10 @@
       <c r="L275" t="n">
         <v>4</v>
       </c>
-      <c r="M275" t="n">
-        <v>4</v>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N275" t="n">
         <v>2</v>
@@ -19094,8 +19456,10 @@
       <c r="L276" t="n">
         <v>4</v>
       </c>
-      <c r="M276" t="n">
-        <v>4</v>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N276" t="n">
         <v>2</v>
@@ -19161,8 +19525,10 @@
       <c r="L277" t="n">
         <v>5</v>
       </c>
-      <c r="M277" t="n">
-        <v>1</v>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N277" t="n">
         <v>2</v>
@@ -19228,8 +19594,10 @@
       <c r="L278" t="n">
         <v>4</v>
       </c>
-      <c r="M278" t="n">
-        <v>4</v>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N278" t="n">
         <v>2</v>
@@ -19295,8 +19663,10 @@
       <c r="L279" t="n">
         <v>4</v>
       </c>
-      <c r="M279" t="n">
-        <v>1</v>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N279" t="n">
         <v>1</v>
@@ -19362,8 +19732,10 @@
       <c r="L280" t="n">
         <v>4</v>
       </c>
-      <c r="M280" t="n">
-        <v>4</v>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N280" t="n">
         <v>2</v>
@@ -19429,8 +19801,10 @@
       <c r="L281" t="n">
         <v>4</v>
       </c>
-      <c r="M281" t="n">
-        <v>2</v>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N281" t="n">
         <v>2</v>
@@ -19496,8 +19870,10 @@
       <c r="L282" t="n">
         <v>5</v>
       </c>
-      <c r="M282" t="n">
-        <v>1</v>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N282" t="n">
         <v>2</v>
@@ -19563,8 +19939,10 @@
       <c r="L283" t="n">
         <v>4</v>
       </c>
-      <c r="M283" t="n">
-        <v>4</v>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N283" t="n">
         <v>2</v>
@@ -19630,8 +20008,10 @@
       <c r="L284" t="n">
         <v>4</v>
       </c>
-      <c r="M284" t="n">
-        <v>4</v>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N284" t="n">
         <v>1</v>
@@ -19697,8 +20077,10 @@
       <c r="L285" t="n">
         <v>2</v>
       </c>
-      <c r="M285" t="n">
-        <v>4</v>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N285" t="n">
         <v>2</v>
@@ -19764,8 +20146,10 @@
       <c r="L286" t="n">
         <v>3</v>
       </c>
-      <c r="M286" t="n">
-        <v>5</v>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N286" t="n">
         <v>2</v>
@@ -19831,8 +20215,10 @@
       <c r="L287" t="n">
         <v>2</v>
       </c>
-      <c r="M287" t="n">
-        <v>4</v>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N287" t="n">
         <v>2</v>
@@ -19898,8 +20284,10 @@
       <c r="L288" t="n">
         <v>3</v>
       </c>
-      <c r="M288" t="n">
-        <v>4</v>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N288" t="n">
         <v>2</v>
@@ -20103,8 +20491,10 @@
       <c r="L291" t="n">
         <v>3</v>
       </c>
-      <c r="M291" t="n">
-        <v>4</v>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N291" t="n">
         <v>2</v>
@@ -20170,8 +20560,10 @@
       <c r="L292" t="n">
         <v>2</v>
       </c>
-      <c r="M292" t="n">
-        <v>4</v>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N292" t="n">
         <v>2</v>
@@ -20237,8 +20629,10 @@
       <c r="L293" t="n">
         <v>3</v>
       </c>
-      <c r="M293" t="n">
-        <v>4</v>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N293" t="n">
         <v>2</v>

--- a/data/split/test.xlsx
+++ b/data/split/test.xlsx
@@ -570,8 +570,10 @@
       <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="M2" t="n">
-        <v>4</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -649,8 +651,10 @@
       <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="M3" t="n">
-        <v>1</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -728,8 +732,10 @@
       <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="n">
-        <v>4</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N4" t="n">
         <v>1</v>
@@ -807,8 +813,10 @@
       <c r="L5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -886,8 +894,10 @@
       <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -965,8 +975,10 @@
       <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>5</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N7" t="n">
         <v>2</v>
@@ -1044,8 +1056,10 @@
       <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
-        <v>1</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -1123,8 +1137,10 @@
       <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>3</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1202,8 +1218,10 @@
       <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
-        <v>4</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1281,8 +1299,10 @@
       <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="n">
-        <v>1</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1522,8 +1542,10 @@
       <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="n">
-        <v>4</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N14" t="n">
         <v>2</v>
@@ -1763,8 +1785,10 @@
       <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="M17" t="n">
-        <v>4</v>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -2004,8 +2028,10 @@
       <c r="L20" t="n">
         <v>4</v>
       </c>
-      <c r="M20" t="n">
-        <v>1</v>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -2083,8 +2109,10 @@
       <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>4</v>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -2243,8 +2271,10 @@
       <c r="L23" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="n">
-        <v>4</v>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2322,8 +2352,10 @@
       <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="M24" t="n">
-        <v>4</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N24" t="n">
         <v>2</v>
@@ -2482,8 +2514,10 @@
       <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M26" t="n">
-        <v>4</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N26" t="n">
         <v>2</v>
@@ -2723,8 +2757,10 @@
       <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="M29" t="n">
-        <v>4</v>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N29" t="n">
         <v>2</v>
@@ -2802,8 +2838,10 @@
       <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="M30" t="n">
-        <v>4</v>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N30" t="n">
         <v>2</v>
@@ -2881,8 +2919,10 @@
       <c r="L31" t="n">
         <v>4</v>
       </c>
-      <c r="M31" t="n">
-        <v>4</v>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N31" t="n">
         <v>2</v>
@@ -3122,8 +3162,10 @@
       <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="n">
-        <v>4</v>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -3201,8 +3243,10 @@
       <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="M35" t="n">
-        <v>5</v>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N35" t="n">
         <v>2</v>
@@ -3280,8 +3324,10 @@
       <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="M36" t="n">
-        <v>4</v>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N36" t="n">
         <v>2</v>
@@ -3440,8 +3486,10 @@
       <c r="L38" t="n">
         <v>4</v>
       </c>
-      <c r="M38" t="n">
-        <v>3</v>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N38" t="n">
         <v>2</v>
@@ -3681,8 +3729,10 @@
       <c r="L41" t="n">
         <v>5</v>
       </c>
-      <c r="M41" t="n">
-        <v>1</v>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3841,8 +3891,10 @@
       <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="M43" t="n">
-        <v>4</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N43" t="n">
         <v>2</v>
@@ -3920,8 +3972,10 @@
       <c r="L44" t="n">
         <v>4</v>
       </c>
-      <c r="M44" t="n">
-        <v>4</v>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N44" t="n">
         <v>2</v>
@@ -3999,8 +4053,10 @@
       <c r="L45" t="n">
         <v>4</v>
       </c>
-      <c r="M45" t="n">
-        <v>4</v>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N45" t="n">
         <v>2</v>
@@ -4078,8 +4134,10 @@
       <c r="L46" t="n">
         <v>5</v>
       </c>
-      <c r="M46" t="n">
-        <v>4</v>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N46" t="n">
         <v>2</v>
@@ -4157,8 +4215,10 @@
       <c r="L47" t="n">
         <v>3</v>
       </c>
-      <c r="M47" t="n">
-        <v>4</v>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N47" t="n">
         <v>2</v>
@@ -4236,8 +4296,10 @@
       <c r="L48" t="n">
         <v>4</v>
       </c>
-      <c r="M48" t="n">
-        <v>4</v>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N48" t="n">
         <v>2</v>
@@ -4477,8 +4539,10 @@
       <c r="L51" t="n">
         <v>5</v>
       </c>
-      <c r="M51" t="n">
-        <v>1</v>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N51" t="n">
         <v>2</v>
@@ -4556,8 +4620,10 @@
       <c r="L52" t="n">
         <v>4</v>
       </c>
-      <c r="M52" t="n">
-        <v>4</v>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N52" t="n">
         <v>2</v>
@@ -4716,8 +4782,10 @@
       <c r="L54" t="n">
         <v>5</v>
       </c>
-      <c r="M54" t="n">
-        <v>2</v>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N54" t="n">
         <v>2</v>
@@ -4876,8 +4944,10 @@
       <c r="L56" t="n">
         <v>4</v>
       </c>
-      <c r="M56" t="n">
-        <v>4</v>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N56" t="n">
         <v>2</v>
@@ -4955,8 +5025,10 @@
       <c r="L57" t="n">
         <v>4</v>
       </c>
-      <c r="M57" t="n">
-        <v>1</v>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N57" t="n">
         <v>1</v>
@@ -5034,8 +5106,10 @@
       <c r="L58" t="n">
         <v>5</v>
       </c>
-      <c r="M58" t="n">
-        <v>1</v>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N58" t="n">
         <v>1</v>
@@ -5113,8 +5187,10 @@
       <c r="L59" t="n">
         <v>3</v>
       </c>
-      <c r="M59" t="n">
-        <v>5</v>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N59" t="n">
         <v>1</v>
@@ -5273,8 +5349,10 @@
       <c r="L61" t="n">
         <v>5</v>
       </c>
-      <c r="M61" t="n">
-        <v>1</v>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N61" t="n">
         <v>1</v>
@@ -5433,8 +5511,10 @@
       <c r="L63" t="n">
         <v>4</v>
       </c>
-      <c r="M63" t="n">
-        <v>5</v>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N63" t="n">
         <v>2</v>
@@ -5512,8 +5592,10 @@
       <c r="L64" t="n">
         <v>2</v>
       </c>
-      <c r="M64" t="n">
-        <v>5</v>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N64" t="n">
         <v>2</v>
@@ -5591,8 +5673,10 @@
       <c r="L65" t="n">
         <v>4</v>
       </c>
-      <c r="M65" t="n">
-        <v>5</v>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N65" t="n">
         <v>2</v>
@@ -5751,8 +5835,10 @@
       <c r="L67" t="n">
         <v>4</v>
       </c>
-      <c r="M67" t="n">
-        <v>5</v>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N67" t="n">
         <v>2</v>
@@ -5830,8 +5916,10 @@
       <c r="L68" t="n">
         <v>2</v>
       </c>
-      <c r="M68" t="n">
-        <v>4</v>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N68" t="n">
         <v>3</v>
@@ -5909,8 +5997,10 @@
       <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="n">
-        <v>5</v>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N69" t="n">
         <v>3</v>
@@ -5988,8 +6078,10 @@
       <c r="L70" t="n">
         <v>4</v>
       </c>
-      <c r="M70" t="n">
-        <v>4</v>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N70" t="n">
         <v>2</v>
@@ -6067,8 +6159,10 @@
       <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="M71" t="n">
-        <v>4</v>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N71" t="n">
         <v>2</v>
@@ -6146,8 +6240,10 @@
       <c r="L72" t="n">
         <v>5</v>
       </c>
-      <c r="M72" t="n">
-        <v>1</v>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N72" t="n">
         <v>2</v>
@@ -6306,8 +6402,10 @@
       <c r="L74" t="n">
         <v>2</v>
       </c>
-      <c r="M74" t="n">
-        <v>3</v>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N74" t="n">
         <v>2</v>
@@ -6385,8 +6483,10 @@
       <c r="L75" t="n">
         <v>4</v>
       </c>
-      <c r="M75" t="n">
-        <v>2</v>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N75" t="n">
         <v>1</v>
@@ -6626,8 +6726,10 @@
       <c r="L78" t="n">
         <v>2</v>
       </c>
-      <c r="M78" t="n">
-        <v>4</v>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N78" t="n">
         <v>2</v>
@@ -6705,8 +6807,10 @@
       <c r="L79" t="n">
         <v>4</v>
       </c>
-      <c r="M79" t="n">
-        <v>4</v>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N79" t="n">
         <v>2</v>
@@ -6784,8 +6888,10 @@
       <c r="L80" t="n">
         <v>4</v>
       </c>
-      <c r="M80" t="n">
-        <v>5</v>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N80" t="n">
         <v>2</v>
@@ -6863,8 +6969,10 @@
       <c r="L81" t="n">
         <v>2</v>
       </c>
-      <c r="M81" t="n">
-        <v>4</v>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N81" t="n">
         <v>2</v>
@@ -6942,8 +7050,10 @@
       <c r="L82" t="n">
         <v>5</v>
       </c>
-      <c r="M82" t="n">
-        <v>4</v>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N82" t="n">
         <v>2</v>
@@ -7021,8 +7131,10 @@
       <c r="L83" t="n">
         <v>4</v>
       </c>
-      <c r="M83" t="n">
-        <v>1</v>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N83" t="n">
         <v>1</v>
@@ -7100,8 +7212,10 @@
       <c r="L84" t="n">
         <v>4</v>
       </c>
-      <c r="M84" t="n">
-        <v>4</v>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N84" t="n">
         <v>1</v>
@@ -7260,8 +7374,10 @@
       <c r="L86" t="n">
         <v>2</v>
       </c>
-      <c r="M86" t="n">
-        <v>4</v>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N86" t="n">
         <v>2</v>
@@ -7339,8 +7455,10 @@
       <c r="L87" t="n">
         <v>2</v>
       </c>
-      <c r="M87" t="n">
-        <v>4</v>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N87" t="n">
         <v>3</v>
@@ -7418,8 +7536,10 @@
       <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="M88" t="n">
-        <v>4</v>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N88" t="n">
         <v>2</v>
@@ -7578,8 +7698,10 @@
       <c r="L90" t="n">
         <v>4</v>
       </c>
-      <c r="M90" t="n">
-        <v>4</v>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N90" t="n">
         <v>2</v>
@@ -7657,8 +7779,10 @@
       <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="M91" t="n">
-        <v>4</v>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N91" t="n">
         <v>2</v>
@@ -7898,8 +8022,10 @@
       <c r="L94" t="n">
         <v>4</v>
       </c>
-      <c r="M94" t="n">
-        <v>4</v>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N94" t="n">
         <v>2</v>
@@ -7977,8 +8103,10 @@
       <c r="L95" t="n">
         <v>5</v>
       </c>
-      <c r="M95" t="n">
-        <v>4</v>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N95" t="n">
         <v>2</v>
@@ -8056,8 +8184,10 @@
       <c r="L96" t="n">
         <v>3</v>
       </c>
-      <c r="M96" t="n">
-        <v>5</v>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N96" t="n">
         <v>2</v>
@@ -8216,8 +8346,10 @@
       <c r="L98" t="n">
         <v>4</v>
       </c>
-      <c r="M98" t="n">
-        <v>4</v>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N98" t="n">
         <v>2</v>
@@ -8295,8 +8427,10 @@
       <c r="L99" t="n">
         <v>5</v>
       </c>
-      <c r="M99" t="n">
-        <v>5</v>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N99" t="n">
         <v>2</v>
@@ -8374,8 +8508,10 @@
       <c r="L100" t="n">
         <v>4</v>
       </c>
-      <c r="M100" t="n">
-        <v>5</v>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N100" t="n">
         <v>2</v>
@@ -8453,8 +8589,10 @@
       <c r="L101" t="n">
         <v>5</v>
       </c>
-      <c r="M101" t="n">
-        <v>3</v>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N101" t="n">
         <v>2</v>
@@ -8694,8 +8832,10 @@
       <c r="L104" t="n">
         <v>5</v>
       </c>
-      <c r="M104" t="n">
-        <v>5</v>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N104" t="n">
         <v>2</v>
@@ -8773,8 +8913,10 @@
       <c r="L105" t="n">
         <v>4</v>
       </c>
-      <c r="M105" t="n">
-        <v>4</v>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N105" t="n">
         <v>2</v>
@@ -8852,8 +8994,10 @@
       <c r="L106" t="n">
         <v>4</v>
       </c>
-      <c r="M106" t="n">
-        <v>4</v>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N106" t="n">
         <v>2</v>
@@ -8931,8 +9075,10 @@
       <c r="L107" t="n">
         <v>4</v>
       </c>
-      <c r="M107" t="n">
-        <v>4</v>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N107" t="n">
         <v>2</v>
@@ -9010,8 +9156,10 @@
       <c r="L108" t="n">
         <v>4</v>
       </c>
-      <c r="M108" t="n">
-        <v>4</v>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N108" t="n">
         <v>2</v>
@@ -9089,8 +9237,10 @@
       <c r="L109" t="n">
         <v>2</v>
       </c>
-      <c r="M109" t="n">
-        <v>4</v>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N109" t="n">
         <v>2</v>
@@ -9249,8 +9399,10 @@
       <c r="L111" t="n">
         <v>5</v>
       </c>
-      <c r="M111" t="n">
-        <v>4</v>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N111" t="n">
         <v>2</v>
@@ -9409,8 +9561,10 @@
       <c r="L113" t="n">
         <v>4</v>
       </c>
-      <c r="M113" t="n">
-        <v>4</v>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N113" t="n">
         <v>2</v>
@@ -9488,8 +9642,10 @@
       <c r="L114" t="n">
         <v>3</v>
       </c>
-      <c r="M114" t="n">
-        <v>4</v>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N114" t="n">
         <v>2</v>
@@ -9567,8 +9723,10 @@
       <c r="L115" t="n">
         <v>2</v>
       </c>
-      <c r="M115" t="n">
-        <v>5</v>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N115" t="n">
         <v>2</v>
@@ -9646,8 +9804,10 @@
       <c r="L116" t="n">
         <v>1</v>
       </c>
-      <c r="M116" t="n">
-        <v>5</v>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N116" t="n">
         <v>2</v>
@@ -9806,8 +9966,10 @@
       <c r="L118" t="n">
         <v>5</v>
       </c>
-      <c r="M118" t="n">
-        <v>4</v>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N118" t="n">
         <v>2</v>
@@ -9885,8 +10047,10 @@
       <c r="L119" t="n">
         <v>2</v>
       </c>
-      <c r="M119" t="n">
-        <v>4</v>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N119" t="n">
         <v>2</v>
@@ -10045,8 +10209,10 @@
       <c r="L121" t="n">
         <v>5</v>
       </c>
-      <c r="M121" t="n">
-        <v>4</v>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N121" t="n">
         <v>2</v>
@@ -10124,8 +10290,10 @@
       <c r="L122" t="n">
         <v>4</v>
       </c>
-      <c r="M122" t="n">
-        <v>5</v>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N122" t="n">
         <v>1</v>
@@ -10203,8 +10371,10 @@
       <c r="L123" t="n">
         <v>3</v>
       </c>
-      <c r="M123" t="n">
-        <v>4</v>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N123" t="n">
         <v>2</v>
@@ -10444,8 +10614,10 @@
       <c r="L126" t="n">
         <v>5</v>
       </c>
-      <c r="M126" t="n">
-        <v>4</v>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N126" t="n">
         <v>2</v>
@@ -10523,8 +10695,10 @@
       <c r="L127" t="n">
         <v>3</v>
       </c>
-      <c r="M127" t="n">
-        <v>1</v>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N127" t="n">
         <v>0</v>
@@ -10683,8 +10857,10 @@
       <c r="L129" t="n">
         <v>2</v>
       </c>
-      <c r="M129" t="n">
-        <v>4</v>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N129" t="n">
         <v>2</v>
@@ -10762,8 +10938,10 @@
       <c r="L130" t="n">
         <v>5</v>
       </c>
-      <c r="M130" t="n">
-        <v>4</v>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N130" t="n">
         <v>2</v>
@@ -10922,8 +11100,10 @@
       <c r="L132" t="n">
         <v>4</v>
       </c>
-      <c r="M132" t="n">
-        <v>4</v>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N132" t="n">
         <v>2</v>
@@ -11001,8 +11181,10 @@
       <c r="L133" t="n">
         <v>5</v>
       </c>
-      <c r="M133" t="n">
-        <v>1</v>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N133" t="n">
         <v>2</v>
@@ -11242,8 +11424,10 @@
       <c r="L136" t="n">
         <v>3</v>
       </c>
-      <c r="M136" t="n">
-        <v>1</v>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N136" t="n">
         <v>2</v>
@@ -11321,8 +11505,10 @@
       <c r="L137" t="n">
         <v>4</v>
       </c>
-      <c r="M137" t="n">
-        <v>4</v>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N137" t="n">
         <v>2</v>
@@ -11400,8 +11586,10 @@
       <c r="L138" t="n">
         <v>4</v>
       </c>
-      <c r="M138" t="n">
-        <v>3</v>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N138" t="n">
         <v>2</v>
@@ -11479,8 +11667,10 @@
       <c r="L139" t="n">
         <v>2</v>
       </c>
-      <c r="M139" t="n">
-        <v>4</v>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N139" t="n">
         <v>2</v>
@@ -11639,8 +11829,10 @@
       <c r="L141" t="n">
         <v>5</v>
       </c>
-      <c r="M141" t="n">
-        <v>4</v>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N141" t="n">
         <v>1</v>
@@ -11718,8 +11910,10 @@
       <c r="L142" t="n">
         <v>5</v>
       </c>
-      <c r="M142" t="n">
-        <v>4</v>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N142" t="n">
         <v>2</v>
@@ -11797,8 +11991,10 @@
       <c r="L143" t="n">
         <v>4</v>
       </c>
-      <c r="M143" t="n">
-        <v>1</v>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N143" t="n">
         <v>0</v>
@@ -12119,8 +12315,10 @@
       <c r="L147" t="n">
         <v>5</v>
       </c>
-      <c r="M147" t="n">
-        <v>4</v>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N147" t="n">
         <v>1</v>
@@ -12198,8 +12396,10 @@
       <c r="L148" t="n">
         <v>4</v>
       </c>
-      <c r="M148" t="n">
-        <v>1</v>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N148" t="n">
         <v>2</v>
@@ -12358,8 +12558,10 @@
       <c r="L150" t="n">
         <v>3</v>
       </c>
-      <c r="M150" t="n">
-        <v>3</v>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N150" t="n">
         <v>2</v>
@@ -12437,8 +12639,10 @@
       <c r="L151" t="n">
         <v>5</v>
       </c>
-      <c r="M151" t="n">
-        <v>4</v>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N151" t="n">
         <v>1</v>
@@ -12678,8 +12882,10 @@
       <c r="L154" t="n">
         <v>4</v>
       </c>
-      <c r="M154" t="n">
-        <v>4</v>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N154" t="n">
         <v>2</v>
@@ -12757,8 +12963,10 @@
       <c r="L155" t="n">
         <v>4</v>
       </c>
-      <c r="M155" t="n">
-        <v>2</v>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N155" t="n">
         <v>2</v>
@@ -12917,8 +13125,10 @@
       <c r="L157" t="n">
         <v>5</v>
       </c>
-      <c r="M157" t="n">
-        <v>4</v>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N157" t="n">
         <v>2</v>
@@ -12996,8 +13206,10 @@
       <c r="L158" t="n">
         <v>4</v>
       </c>
-      <c r="M158" t="n">
-        <v>5</v>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N158" t="n">
         <v>2</v>
@@ -13075,8 +13287,10 @@
       <c r="L159" t="n">
         <v>3</v>
       </c>
-      <c r="M159" t="n">
-        <v>4</v>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N159" t="n">
         <v>2</v>
@@ -13316,8 +13530,10 @@
       <c r="L162" t="n">
         <v>5</v>
       </c>
-      <c r="M162" t="n">
-        <v>1</v>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N162" t="n">
         <v>1</v>
@@ -13395,8 +13611,10 @@
       <c r="L163" t="n">
         <v>4</v>
       </c>
-      <c r="M163" t="n">
-        <v>4</v>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N163" t="n">
         <v>2</v>
@@ -13474,8 +13692,10 @@
       <c r="L164" t="n">
         <v>4</v>
       </c>
-      <c r="M164" t="n">
-        <v>4</v>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N164" t="n">
         <v>2</v>
@@ -13553,8 +13773,10 @@
       <c r="L165" t="n">
         <v>2</v>
       </c>
-      <c r="M165" t="n">
-        <v>4</v>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N165" t="n">
         <v>2</v>
@@ -13632,8 +13854,10 @@
       <c r="L166" t="n">
         <v>5</v>
       </c>
-      <c r="M166" t="n">
-        <v>4</v>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N166" t="n">
         <v>1</v>
@@ -13711,8 +13935,10 @@
       <c r="L167" t="n">
         <v>2</v>
       </c>
-      <c r="M167" t="n">
-        <v>4</v>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N167" t="n">
         <v>0</v>
@@ -13790,8 +14016,10 @@
       <c r="L168" t="n">
         <v>5</v>
       </c>
-      <c r="M168" t="n">
-        <v>1</v>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N168" t="n">
         <v>2</v>
@@ -13950,8 +14178,10 @@
       <c r="L170" t="n">
         <v>4</v>
       </c>
-      <c r="M170" t="n">
-        <v>4</v>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N170" t="n">
         <v>2</v>
@@ -14029,8 +14259,10 @@
       <c r="L171" t="n">
         <v>4</v>
       </c>
-      <c r="M171" t="n">
-        <v>4</v>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N171" t="n">
         <v>2</v>
@@ -14108,8 +14340,10 @@
       <c r="L172" t="n">
         <v>4</v>
       </c>
-      <c r="M172" t="n">
-        <v>4</v>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N172" t="n">
         <v>0</v>
@@ -14268,8 +14502,10 @@
       <c r="L174" t="n">
         <v>4</v>
       </c>
-      <c r="M174" t="n">
-        <v>4</v>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N174" t="n">
         <v>2</v>
@@ -14590,8 +14826,10 @@
       <c r="L178" t="n">
         <v>2</v>
       </c>
-      <c r="M178" t="n">
-        <v>5</v>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N178" t="n">
         <v>2</v>
@@ -14669,8 +14907,10 @@
       <c r="L179" t="n">
         <v>4</v>
       </c>
-      <c r="M179" t="n">
-        <v>4</v>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N179" t="n">
         <v>2</v>
@@ -14829,8 +15069,10 @@
       <c r="L181" t="n">
         <v>4</v>
       </c>
-      <c r="M181" t="n">
-        <v>5</v>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N181" t="n">
         <v>2</v>
@@ -14908,8 +15150,10 @@
       <c r="L182" t="n">
         <v>5</v>
       </c>
-      <c r="M182" t="n">
-        <v>5</v>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N182" t="n">
         <v>2</v>
@@ -14987,8 +15231,10 @@
       <c r="L183" t="n">
         <v>3</v>
       </c>
-      <c r="M183" t="n">
-        <v>4</v>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N183" t="n">
         <v>2</v>
@@ -15066,8 +15312,10 @@
       <c r="L184" t="n">
         <v>4</v>
       </c>
-      <c r="M184" t="n">
-        <v>5</v>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N184" t="n">
         <v>1</v>
@@ -15388,8 +15636,10 @@
       <c r="L188" t="n">
         <v>2</v>
       </c>
-      <c r="M188" t="n">
-        <v>4</v>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N188" t="n">
         <v>3</v>
@@ -15548,8 +15798,10 @@
       <c r="L190" t="n">
         <v>2</v>
       </c>
-      <c r="M190" t="n">
-        <v>4</v>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N190" t="n">
         <v>3</v>
@@ -15627,8 +15879,10 @@
       <c r="L191" t="n">
         <v>3</v>
       </c>
-      <c r="M191" t="n">
-        <v>4</v>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N191" t="n">
         <v>2</v>
@@ -15706,8 +15960,10 @@
       <c r="L192" t="n">
         <v>5</v>
       </c>
-      <c r="M192" t="n">
-        <v>1</v>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N192" t="n">
         <v>2</v>
@@ -15785,8 +16041,10 @@
       <c r="L193" t="n">
         <v>4</v>
       </c>
-      <c r="M193" t="n">
-        <v>4</v>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N193" t="n">
         <v>2</v>
@@ -15945,8 +16203,10 @@
       <c r="L195" t="n">
         <v>3</v>
       </c>
-      <c r="M195" t="n">
-        <v>4</v>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N195" t="n">
         <v>2</v>
@@ -16024,8 +16284,10 @@
       <c r="L196" t="n">
         <v>5</v>
       </c>
-      <c r="M196" t="n">
-        <v>4</v>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N196" t="n">
         <v>2</v>
@@ -16184,8 +16446,10 @@
       <c r="L198" t="n">
         <v>2</v>
       </c>
-      <c r="M198" t="n">
-        <v>4</v>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N198" t="n">
         <v>2</v>
@@ -16344,8 +16608,10 @@
       <c r="L200" t="n">
         <v>4</v>
       </c>
-      <c r="M200" t="n">
-        <v>4</v>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N200" t="n">
         <v>2</v>
@@ -16423,8 +16689,10 @@
       <c r="L201" t="n">
         <v>4</v>
       </c>
-      <c r="M201" t="n">
-        <v>4</v>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N201" t="n">
         <v>2</v>
@@ -16502,8 +16770,10 @@
       <c r="L202" t="n">
         <v>2</v>
       </c>
-      <c r="M202" t="n">
-        <v>4</v>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N202" t="n">
         <v>1</v>
@@ -16581,8 +16851,10 @@
       <c r="L203" t="n">
         <v>5</v>
       </c>
-      <c r="M203" t="n">
-        <v>1</v>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N203" t="n">
         <v>1</v>
@@ -16741,8 +17013,10 @@
       <c r="L205" t="n">
         <v>3</v>
       </c>
-      <c r="M205" t="n">
-        <v>4</v>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N205" t="n">
         <v>2</v>
@@ -16901,8 +17175,10 @@
       <c r="L207" t="n">
         <v>4</v>
       </c>
-      <c r="M207" t="n">
-        <v>4</v>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N207" t="n">
         <v>2</v>
@@ -17061,8 +17337,10 @@
       <c r="L209" t="n">
         <v>2</v>
       </c>
-      <c r="M209" t="n">
-        <v>4</v>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N209" t="n">
         <v>3</v>
@@ -17221,8 +17499,10 @@
       <c r="L211" t="n">
         <v>4</v>
       </c>
-      <c r="M211" t="n">
-        <v>4</v>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N211" t="n">
         <v>2</v>
@@ -17300,8 +17580,10 @@
       <c r="L212" t="n">
         <v>2</v>
       </c>
-      <c r="M212" t="n">
-        <v>4</v>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N212" t="n">
         <v>2</v>
@@ -17379,8 +17661,10 @@
       <c r="L213" t="n">
         <v>4</v>
       </c>
-      <c r="M213" t="n">
-        <v>4</v>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N213" t="n">
         <v>2</v>
@@ -17458,8 +17742,10 @@
       <c r="L214" t="n">
         <v>4</v>
       </c>
-      <c r="M214" t="n">
-        <v>5</v>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N214" t="n">
         <v>2</v>
@@ -17699,8 +17985,10 @@
       <c r="L217" t="n">
         <v>5</v>
       </c>
-      <c r="M217" t="n">
-        <v>4</v>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N217" t="n">
         <v>2</v>
@@ -17859,8 +18147,10 @@
       <c r="L219" t="n">
         <v>5</v>
       </c>
-      <c r="M219" t="n">
-        <v>5</v>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N219" t="n">
         <v>2</v>
@@ -17938,8 +18228,10 @@
       <c r="L220" t="n">
         <v>5</v>
       </c>
-      <c r="M220" t="n">
-        <v>4</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N220" t="n">
         <v>2</v>
@@ -18098,8 +18390,10 @@
       <c r="L222" t="n">
         <v>2</v>
       </c>
-      <c r="M222" t="n">
-        <v>4</v>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N222" t="n">
         <v>3</v>
@@ -18258,8 +18552,10 @@
       <c r="L224" t="n">
         <v>3</v>
       </c>
-      <c r="M224" t="n">
-        <v>5</v>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N224" t="n">
         <v>2</v>
@@ -18337,8 +18633,10 @@
       <c r="L225" t="n">
         <v>4</v>
       </c>
-      <c r="M225" t="n">
-        <v>4</v>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N225" t="n">
         <v>2</v>
@@ -18497,8 +18795,10 @@
       <c r="L227" t="n">
         <v>4</v>
       </c>
-      <c r="M227" t="n">
-        <v>4</v>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N227" t="n">
         <v>2</v>
@@ -18576,8 +18876,10 @@
       <c r="L228" t="n">
         <v>4</v>
       </c>
-      <c r="M228" t="n">
-        <v>4</v>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N228" t="n">
         <v>2</v>
@@ -18655,8 +18957,10 @@
       <c r="L229" t="n">
         <v>3</v>
       </c>
-      <c r="M229" t="n">
-        <v>5</v>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N229" t="n">
         <v>2</v>
@@ -18977,8 +19281,10 @@
       <c r="L233" t="n">
         <v>2</v>
       </c>
-      <c r="M233" t="n">
-        <v>4</v>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N233" t="n">
         <v>2</v>
@@ -19380,8 +19686,10 @@
       <c r="L238" t="n">
         <v>4</v>
       </c>
-      <c r="M238" t="n">
-        <v>4</v>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N238" t="n">
         <v>2</v>
@@ -19459,8 +19767,10 @@
       <c r="L239" t="n">
         <v>5</v>
       </c>
-      <c r="M239" t="n">
-        <v>4</v>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N239" t="n">
         <v>2</v>
@@ -19619,8 +19929,10 @@
       <c r="L241" t="n">
         <v>4</v>
       </c>
-      <c r="M241" t="n">
-        <v>4</v>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N241" t="n">
         <v>2</v>
@@ -19698,8 +20010,10 @@
       <c r="L242" t="n">
         <v>4</v>
       </c>
-      <c r="M242" t="n">
-        <v>4</v>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N242" t="n">
         <v>1</v>
@@ -19777,8 +20091,10 @@
       <c r="L243" t="n">
         <v>4</v>
       </c>
-      <c r="M243" t="n">
-        <v>3</v>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N243" t="n">
         <v>0</v>
@@ -19856,8 +20172,10 @@
       <c r="L244" t="n">
         <v>4</v>
       </c>
-      <c r="M244" t="n">
-        <v>1</v>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N244" t="n">
         <v>1</v>
@@ -20016,8 +20334,10 @@
       <c r="L246" t="n">
         <v>4</v>
       </c>
-      <c r="M246" t="n">
-        <v>4</v>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N246" t="n">
         <v>2</v>
@@ -20095,8 +20415,10 @@
       <c r="L247" t="n">
         <v>3</v>
       </c>
-      <c r="M247" t="n">
-        <v>5</v>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N247" t="n">
         <v>2</v>
@@ -20174,8 +20496,10 @@
       <c r="L248" t="n">
         <v>2</v>
       </c>
-      <c r="M248" t="n">
-        <v>4</v>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N248" t="n">
         <v>2</v>
@@ -20415,8 +20739,10 @@
       <c r="L251" t="n">
         <v>4</v>
       </c>
-      <c r="M251" t="n">
-        <v>4</v>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N251" t="n">
         <v>2</v>
@@ -20494,8 +20820,10 @@
       <c r="L252" t="n">
         <v>4</v>
       </c>
-      <c r="M252" t="n">
-        <v>4</v>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N252" t="n">
         <v>2</v>
@@ -20573,8 +20901,10 @@
       <c r="L253" t="n">
         <v>4</v>
       </c>
-      <c r="M253" t="n">
-        <v>4</v>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N253" t="n">
         <v>1</v>
@@ -20895,8 +21225,10 @@
       <c r="L257" t="n">
         <v>4</v>
       </c>
-      <c r="M257" t="n">
-        <v>5</v>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N257" t="n">
         <v>1</v>
@@ -20974,8 +21306,10 @@
       <c r="L258" t="n">
         <v>4</v>
       </c>
-      <c r="M258" t="n">
-        <v>5</v>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N258" t="n">
         <v>2</v>
@@ -21053,8 +21387,10 @@
       <c r="L259" t="n">
         <v>5</v>
       </c>
-      <c r="M259" t="n">
-        <v>4</v>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N259" t="n">
         <v>0</v>
@@ -21132,8 +21468,10 @@
       <c r="L260" t="n">
         <v>2</v>
       </c>
-      <c r="M260" t="n">
-        <v>4</v>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N260" t="n">
         <v>2</v>
@@ -21211,8 +21549,10 @@
       <c r="L261" t="n">
         <v>5</v>
       </c>
-      <c r="M261" t="n">
-        <v>1</v>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N261" t="n">
         <v>2</v>
@@ -21290,8 +21630,10 @@
       <c r="L262" t="n">
         <v>4</v>
       </c>
-      <c r="M262" t="n">
-        <v>1</v>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N262" t="n">
         <v>2</v>
@@ -21369,8 +21711,10 @@
       <c r="L263" t="n">
         <v>5</v>
       </c>
-      <c r="M263" t="n">
-        <v>1</v>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N263" t="n">
         <v>2</v>
@@ -21448,8 +21792,10 @@
       <c r="L264" t="n">
         <v>4</v>
       </c>
-      <c r="M264" t="n">
-        <v>4</v>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N264" t="n">
         <v>2</v>
@@ -21608,8 +21954,10 @@
       <c r="L266" t="n">
         <v>5</v>
       </c>
-      <c r="M266" t="n">
-        <v>5</v>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N266" t="n">
         <v>2</v>
@@ -21687,8 +22035,10 @@
       <c r="L267" t="n">
         <v>3</v>
       </c>
-      <c r="M267" t="n">
-        <v>4</v>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N267" t="n">
         <v>2</v>
@@ -21766,8 +22116,10 @@
       <c r="L268" t="n">
         <v>4</v>
       </c>
-      <c r="M268" t="n">
-        <v>2</v>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N268" t="n">
         <v>2</v>
@@ -21845,8 +22197,10 @@
       <c r="L269" t="n">
         <v>4</v>
       </c>
-      <c r="M269" t="n">
-        <v>5</v>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N269" t="n">
         <v>2</v>
@@ -22005,8 +22359,10 @@
       <c r="L271" t="n">
         <v>5</v>
       </c>
-      <c r="M271" t="n">
-        <v>4</v>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N271" t="n">
         <v>2</v>
@@ -22084,8 +22440,10 @@
       <c r="L272" t="n">
         <v>5</v>
       </c>
-      <c r="M272" t="n">
-        <v>5</v>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N272" t="n">
         <v>2</v>
@@ -22163,8 +22521,10 @@
       <c r="L273" t="n">
         <v>4</v>
       </c>
-      <c r="M273" t="n">
-        <v>4</v>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N273" t="n">
         <v>2</v>
@@ -22323,8 +22683,10 @@
       <c r="L275" t="n">
         <v>4</v>
       </c>
-      <c r="M275" t="n">
-        <v>4</v>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N275" t="n">
         <v>2</v>
@@ -22402,8 +22764,10 @@
       <c r="L276" t="n">
         <v>4</v>
       </c>
-      <c r="M276" t="n">
-        <v>4</v>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N276" t="n">
         <v>2</v>
@@ -22481,8 +22845,10 @@
       <c r="L277" t="n">
         <v>5</v>
       </c>
-      <c r="M277" t="n">
-        <v>1</v>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N277" t="n">
         <v>2</v>
@@ -22560,8 +22926,10 @@
       <c r="L278" t="n">
         <v>4</v>
       </c>
-      <c r="M278" t="n">
-        <v>4</v>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N278" t="n">
         <v>2</v>
@@ -22639,8 +23007,10 @@
       <c r="L279" t="n">
         <v>4</v>
       </c>
-      <c r="M279" t="n">
-        <v>1</v>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N279" t="n">
         <v>1</v>
@@ -22718,8 +23088,10 @@
       <c r="L280" t="n">
         <v>4</v>
       </c>
-      <c r="M280" t="n">
-        <v>4</v>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N280" t="n">
         <v>2</v>
@@ -22797,8 +23169,10 @@
       <c r="L281" t="n">
         <v>4</v>
       </c>
-      <c r="M281" t="n">
-        <v>2</v>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N281" t="n">
         <v>2</v>
@@ -22876,8 +23250,10 @@
       <c r="L282" t="n">
         <v>5</v>
       </c>
-      <c r="M282" t="n">
-        <v>1</v>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N282" t="n">
         <v>2</v>
@@ -22955,8 +23331,10 @@
       <c r="L283" t="n">
         <v>4</v>
       </c>
-      <c r="M283" t="n">
-        <v>4</v>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N283" t="n">
         <v>2</v>
@@ -23034,8 +23412,10 @@
       <c r="L284" t="n">
         <v>4</v>
       </c>
-      <c r="M284" t="n">
-        <v>4</v>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N284" t="n">
         <v>1</v>
@@ -23113,8 +23493,10 @@
       <c r="L285" t="n">
         <v>2</v>
       </c>
-      <c r="M285" t="n">
-        <v>4</v>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N285" t="n">
         <v>2</v>
@@ -23192,8 +23574,10 @@
       <c r="L286" t="n">
         <v>3</v>
       </c>
-      <c r="M286" t="n">
-        <v>5</v>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N286" t="n">
         <v>2</v>
@@ -23271,8 +23655,10 @@
       <c r="L287" t="n">
         <v>2</v>
       </c>
-      <c r="M287" t="n">
-        <v>4</v>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N287" t="n">
         <v>2</v>
@@ -23350,8 +23736,10 @@
       <c r="L288" t="n">
         <v>3</v>
       </c>
-      <c r="M288" t="n">
-        <v>4</v>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N288" t="n">
         <v>2</v>
@@ -23591,8 +23979,10 @@
       <c r="L291" t="n">
         <v>3</v>
       </c>
-      <c r="M291" t="n">
-        <v>4</v>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N291" t="n">
         <v>2</v>
@@ -23670,8 +24060,10 @@
       <c r="L292" t="n">
         <v>2</v>
       </c>
-      <c r="M292" t="n">
-        <v>4</v>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N292" t="n">
         <v>2</v>
@@ -23749,8 +24141,10 @@
       <c r="L293" t="n">
         <v>3</v>
       </c>
-      <c r="M293" t="n">
-        <v>4</v>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N293" t="n">
         <v>2</v>

--- a/data/split/test.xlsx
+++ b/data/split/test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W294"/>
+  <dimension ref="A1:X294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,11 @@
           <t>pass_loc_sin</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>men</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -570,10 +575,8 @@
       <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M2" t="n">
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -612,6 +615,9 @@
       </c>
       <c r="W2" t="n">
         <v>1</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -651,10 +657,8 @@
       <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M3" t="n">
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -693,6 +697,9 @@
       </c>
       <c r="W3" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -732,10 +739,8 @@
       <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M4" t="n">
+        <v>4</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
@@ -774,6 +779,9 @@
       </c>
       <c r="W4" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -813,10 +821,8 @@
       <c r="L5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M5" t="n">
+        <v>4</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -855,6 +861,9 @@
       </c>
       <c r="W5" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -894,10 +903,8 @@
       <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M6" t="n">
+        <v>4</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -936,6 +943,9 @@
       </c>
       <c r="W6" t="n">
         <v>1</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -975,10 +985,8 @@
       <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M7" t="n">
+        <v>5</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
@@ -1017,6 +1025,9 @@
       </c>
       <c r="W7" t="n">
         <v>-1</v>
+      </c>
+      <c r="X7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1056,10 +1067,8 @@
       <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M8" t="n">
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -1098,6 +1107,9 @@
       </c>
       <c r="W8" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1137,10 +1149,8 @@
       <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M9" t="n">
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1179,6 +1189,9 @@
       </c>
       <c r="W9" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1218,10 +1231,8 @@
       <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M10" t="n">
+        <v>4</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1260,6 +1271,9 @@
       </c>
       <c r="W10" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1299,10 +1313,8 @@
       <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M11" t="n">
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1341,6 +1353,9 @@
       </c>
       <c r="W11" t="n">
         <v>-1</v>
+      </c>
+      <c r="X11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1423,6 +1438,9 @@
       <c r="W12" t="n">
         <v>-1</v>
       </c>
+      <c r="X12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1504,6 +1522,9 @@
       <c r="W13" t="n">
         <v>-1</v>
       </c>
+      <c r="X13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1542,10 +1563,8 @@
       <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M14" t="n">
+        <v>4</v>
       </c>
       <c r="N14" t="n">
         <v>2</v>
@@ -1584,6 +1603,9 @@
       </c>
       <c r="W14" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1666,6 +1688,9 @@
       <c r="W15" t="n">
         <v>-1</v>
       </c>
+      <c r="X15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1747,6 +1772,9 @@
       <c r="W16" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1785,10 +1813,8 @@
       <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M17" t="n">
+        <v>4</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -1827,6 +1853,9 @@
       </c>
       <c r="W17" t="n">
         <v>-1</v>
+      </c>
+      <c r="X17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1909,6 +1938,9 @@
       <c r="W18" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1990,6 +2022,9 @@
       <c r="W19" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2028,10 +2063,8 @@
       <c r="L20" t="n">
         <v>4</v>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M20" t="n">
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -2070,6 +2103,9 @@
       </c>
       <c r="W20" t="n">
         <v>-1</v>
+      </c>
+      <c r="X20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2109,10 +2145,8 @@
       <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M21" t="n">
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -2151,6 +2185,9 @@
       </c>
       <c r="W21" t="n">
         <v>-1</v>
+      </c>
+      <c r="X21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2233,6 +2270,9 @@
       <c r="W22" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2271,10 +2311,8 @@
       <c r="L23" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M23" t="n">
+        <v>4</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2313,6 +2351,9 @@
       </c>
       <c r="W23" t="n">
         <v>-1</v>
+      </c>
+      <c r="X23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2352,10 +2393,8 @@
       <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M24" t="n">
+        <v>4</v>
       </c>
       <c r="N24" t="n">
         <v>2</v>
@@ -2394,6 +2433,9 @@
       </c>
       <c r="W24" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2476,6 +2518,9 @@
       <c r="W25" t="n">
         <v>-1</v>
       </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2514,10 +2559,8 @@
       <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M26" t="n">
+        <v>4</v>
       </c>
       <c r="N26" t="n">
         <v>2</v>
@@ -2556,6 +2599,9 @@
       </c>
       <c r="W26" t="n">
         <v>-1</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2638,6 +2684,9 @@
       <c r="W27" t="n">
         <v>-1</v>
       </c>
+      <c r="X27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2719,6 +2768,9 @@
       <c r="W28" t="n">
         <v>-1</v>
       </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2757,10 +2809,8 @@
       <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M29" t="n">
+        <v>4</v>
       </c>
       <c r="N29" t="n">
         <v>2</v>
@@ -2799,6 +2849,9 @@
       </c>
       <c r="W29" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2838,10 +2891,8 @@
       <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M30" t="n">
+        <v>4</v>
       </c>
       <c r="N30" t="n">
         <v>2</v>
@@ -2880,6 +2931,9 @@
       </c>
       <c r="W30" t="n">
         <v>-1</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2919,10 +2973,8 @@
       <c r="L31" t="n">
         <v>4</v>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M31" t="n">
+        <v>4</v>
       </c>
       <c r="N31" t="n">
         <v>2</v>
@@ -2961,6 +3013,9 @@
       </c>
       <c r="W31" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3043,6 +3098,9 @@
       <c r="W32" t="n">
         <v>-1</v>
       </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3124,6 +3182,9 @@
       <c r="W33" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3162,10 +3223,8 @@
       <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M34" t="n">
+        <v>4</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -3204,6 +3263,9 @@
       </c>
       <c r="W34" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3243,10 +3305,8 @@
       <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M35" t="n">
+        <v>5</v>
       </c>
       <c r="N35" t="n">
         <v>2</v>
@@ -3285,6 +3345,9 @@
       </c>
       <c r="W35" t="n">
         <v>-1</v>
+      </c>
+      <c r="X35" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3324,10 +3387,8 @@
       <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M36" t="n">
+        <v>4</v>
       </c>
       <c r="N36" t="n">
         <v>2</v>
@@ -3366,6 +3427,9 @@
       </c>
       <c r="W36" t="n">
         <v>1</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3448,6 +3512,9 @@
       <c r="W37" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3486,10 +3553,8 @@
       <c r="L38" t="n">
         <v>4</v>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M38" t="n">
+        <v>3</v>
       </c>
       <c r="N38" t="n">
         <v>2</v>
@@ -3528,6 +3593,9 @@
       </c>
       <c r="W38" t="n">
         <v>-1</v>
+      </c>
+      <c r="X38" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3610,6 +3678,9 @@
       <c r="W39" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3691,6 +3762,9 @@
       <c r="W40" t="n">
         <v>-1</v>
       </c>
+      <c r="X40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3729,10 +3803,8 @@
       <c r="L41" t="n">
         <v>5</v>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M41" t="n">
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3771,6 +3843,9 @@
       </c>
       <c r="W41" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3853,6 +3928,9 @@
       <c r="W42" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3891,10 +3969,8 @@
       <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M43" t="n">
+        <v>4</v>
       </c>
       <c r="N43" t="n">
         <v>2</v>
@@ -3933,6 +4009,9 @@
       </c>
       <c r="W43" t="n">
         <v>1</v>
+      </c>
+      <c r="X43" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3972,10 +4051,8 @@
       <c r="L44" t="n">
         <v>4</v>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M44" t="n">
+        <v>4</v>
       </c>
       <c r="N44" t="n">
         <v>2</v>
@@ -4014,6 +4091,9 @@
       </c>
       <c r="W44" t="n">
         <v>-1</v>
+      </c>
+      <c r="X44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4053,10 +4133,8 @@
       <c r="L45" t="n">
         <v>4</v>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M45" t="n">
+        <v>4</v>
       </c>
       <c r="N45" t="n">
         <v>2</v>
@@ -4095,6 +4173,9 @@
       </c>
       <c r="W45" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4134,10 +4215,8 @@
       <c r="L46" t="n">
         <v>5</v>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M46" t="n">
+        <v>4</v>
       </c>
       <c r="N46" t="n">
         <v>2</v>
@@ -4176,6 +4255,9 @@
       </c>
       <c r="W46" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4215,10 +4297,8 @@
       <c r="L47" t="n">
         <v>3</v>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M47" t="n">
+        <v>4</v>
       </c>
       <c r="N47" t="n">
         <v>2</v>
@@ -4257,6 +4337,9 @@
       </c>
       <c r="W47" t="n">
         <v>-1</v>
+      </c>
+      <c r="X47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4296,10 +4379,8 @@
       <c r="L48" t="n">
         <v>4</v>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M48" t="n">
+        <v>4</v>
       </c>
       <c r="N48" t="n">
         <v>2</v>
@@ -4337,6 +4418,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4420,6 +4504,9 @@
       <c r="W49" t="n">
         <v>-1</v>
       </c>
+      <c r="X49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4501,6 +4588,9 @@
       <c r="W50" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4539,10 +4629,8 @@
       <c r="L51" t="n">
         <v>5</v>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M51" t="n">
+        <v>1</v>
       </c>
       <c r="N51" t="n">
         <v>2</v>
@@ -4581,6 +4669,9 @@
       </c>
       <c r="W51" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4620,10 +4711,8 @@
       <c r="L52" t="n">
         <v>4</v>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M52" t="n">
+        <v>4</v>
       </c>
       <c r="N52" t="n">
         <v>2</v>
@@ -4662,6 +4751,9 @@
       </c>
       <c r="W52" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X52" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4744,6 +4836,9 @@
       <c r="W53" t="n">
         <v>-1</v>
       </c>
+      <c r="X53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4782,10 +4877,8 @@
       <c r="L54" t="n">
         <v>5</v>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="M54" t="n">
+        <v>2</v>
       </c>
       <c r="N54" t="n">
         <v>2</v>
@@ -4824,6 +4917,9 @@
       </c>
       <c r="W54" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X54" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -4906,6 +5002,9 @@
       <c r="W55" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4944,10 +5043,8 @@
       <c r="L56" t="n">
         <v>4</v>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M56" t="n">
+        <v>4</v>
       </c>
       <c r="N56" t="n">
         <v>2</v>
@@ -4986,6 +5083,9 @@
       </c>
       <c r="W56" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5025,10 +5125,8 @@
       <c r="L57" t="n">
         <v>4</v>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M57" t="n">
+        <v>1</v>
       </c>
       <c r="N57" t="n">
         <v>1</v>
@@ -5067,6 +5165,9 @@
       </c>
       <c r="W57" t="n">
         <v>-1</v>
+      </c>
+      <c r="X57" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5106,10 +5207,8 @@
       <c r="L58" t="n">
         <v>5</v>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M58" t="n">
+        <v>1</v>
       </c>
       <c r="N58" t="n">
         <v>1</v>
@@ -5148,6 +5247,9 @@
       </c>
       <c r="W58" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X58" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -5187,10 +5289,8 @@
       <c r="L59" t="n">
         <v>3</v>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M59" t="n">
+        <v>5</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
@@ -5229,6 +5329,9 @@
       </c>
       <c r="W59" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X59" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5311,6 +5414,9 @@
       <c r="W60" t="n">
         <v>-1</v>
       </c>
+      <c r="X60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5349,10 +5455,8 @@
       <c r="L61" t="n">
         <v>5</v>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M61" t="n">
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>1</v>
@@ -5391,6 +5495,9 @@
       </c>
       <c r="W61" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X61" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5473,6 +5580,9 @@
       <c r="W62" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X62" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5511,10 +5621,8 @@
       <c r="L63" t="n">
         <v>4</v>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M63" t="n">
+        <v>5</v>
       </c>
       <c r="N63" t="n">
         <v>2</v>
@@ -5553,6 +5661,9 @@
       </c>
       <c r="W63" t="n">
         <v>1</v>
+      </c>
+      <c r="X63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5592,10 +5703,8 @@
       <c r="L64" t="n">
         <v>2</v>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M64" t="n">
+        <v>5</v>
       </c>
       <c r="N64" t="n">
         <v>2</v>
@@ -5634,6 +5743,9 @@
       </c>
       <c r="W64" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5673,10 +5785,8 @@
       <c r="L65" t="n">
         <v>4</v>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M65" t="n">
+        <v>5</v>
       </c>
       <c r="N65" t="n">
         <v>2</v>
@@ -5715,6 +5825,9 @@
       </c>
       <c r="W65" t="n">
         <v>-1</v>
+      </c>
+      <c r="X65" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -5797,6 +5910,9 @@
       <c r="W66" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X66" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5835,10 +5951,8 @@
       <c r="L67" t="n">
         <v>4</v>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M67" t="n">
+        <v>5</v>
       </c>
       <c r="N67" t="n">
         <v>2</v>
@@ -5877,6 +5991,9 @@
       </c>
       <c r="W67" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X67" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5916,10 +6033,8 @@
       <c r="L68" t="n">
         <v>2</v>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M68" t="n">
+        <v>4</v>
       </c>
       <c r="N68" t="n">
         <v>3</v>
@@ -5958,6 +6073,9 @@
       </c>
       <c r="W68" t="n">
         <v>-1</v>
+      </c>
+      <c r="X68" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -5997,10 +6115,8 @@
       <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M69" t="n">
+        <v>5</v>
       </c>
       <c r="N69" t="n">
         <v>3</v>
@@ -6038,6 +6154,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W69" t="n">
+        <v>1</v>
+      </c>
+      <c r="X69" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6078,10 +6197,8 @@
       <c r="L70" t="n">
         <v>4</v>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M70" t="n">
+        <v>4</v>
       </c>
       <c r="N70" t="n">
         <v>2</v>
@@ -6119,6 +6236,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6159,10 +6279,8 @@
       <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M71" t="n">
+        <v>4</v>
       </c>
       <c r="N71" t="n">
         <v>2</v>
@@ -6201,6 +6319,9 @@
       </c>
       <c r="W71" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X71" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6240,10 +6361,8 @@
       <c r="L72" t="n">
         <v>5</v>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M72" t="n">
+        <v>1</v>
       </c>
       <c r="N72" t="n">
         <v>2</v>
@@ -6282,6 +6401,9 @@
       </c>
       <c r="W72" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X72" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6364,6 +6486,9 @@
       <c r="W73" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6402,10 +6527,8 @@
       <c r="L74" t="n">
         <v>2</v>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M74" t="n">
+        <v>3</v>
       </c>
       <c r="N74" t="n">
         <v>2</v>
@@ -6444,6 +6567,9 @@
       </c>
       <c r="W74" t="n">
         <v>1</v>
+      </c>
+      <c r="X74" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6483,10 +6609,8 @@
       <c r="L75" t="n">
         <v>4</v>
       </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="M75" t="n">
+        <v>2</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
@@ -6525,6 +6649,9 @@
       </c>
       <c r="W75" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X75" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -6607,6 +6734,9 @@
       <c r="W76" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X76" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6688,6 +6818,9 @@
       <c r="W77" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X77" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6726,10 +6859,8 @@
       <c r="L78" t="n">
         <v>2</v>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M78" t="n">
+        <v>4</v>
       </c>
       <c r="N78" t="n">
         <v>2</v>
@@ -6768,6 +6899,9 @@
       </c>
       <c r="W78" t="n">
         <v>1</v>
+      </c>
+      <c r="X78" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6807,10 +6941,8 @@
       <c r="L79" t="n">
         <v>4</v>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M79" t="n">
+        <v>4</v>
       </c>
       <c r="N79" t="n">
         <v>2</v>
@@ -6849,6 +6981,9 @@
       </c>
       <c r="W79" t="n">
         <v>-1</v>
+      </c>
+      <c r="X79" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -6888,10 +7023,8 @@
       <c r="L80" t="n">
         <v>4</v>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M80" t="n">
+        <v>5</v>
       </c>
       <c r="N80" t="n">
         <v>2</v>
@@ -6930,6 +7063,9 @@
       </c>
       <c r="W80" t="n">
         <v>-1</v>
+      </c>
+      <c r="X80" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6969,10 +7105,8 @@
       <c r="L81" t="n">
         <v>2</v>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M81" t="n">
+        <v>4</v>
       </c>
       <c r="N81" t="n">
         <v>2</v>
@@ -7011,6 +7145,9 @@
       </c>
       <c r="W81" t="n">
         <v>-1</v>
+      </c>
+      <c r="X81" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -7050,10 +7187,8 @@
       <c r="L82" t="n">
         <v>5</v>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M82" t="n">
+        <v>4</v>
       </c>
       <c r="N82" t="n">
         <v>2</v>
@@ -7092,6 +7227,9 @@
       </c>
       <c r="W82" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X82" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -7131,10 +7269,8 @@
       <c r="L83" t="n">
         <v>4</v>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M83" t="n">
+        <v>1</v>
       </c>
       <c r="N83" t="n">
         <v>1</v>
@@ -7173,6 +7309,9 @@
       </c>
       <c r="W83" t="n">
         <v>-1</v>
+      </c>
+      <c r="X83" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -7212,10 +7351,8 @@
       <c r="L84" t="n">
         <v>4</v>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M84" t="n">
+        <v>4</v>
       </c>
       <c r="N84" t="n">
         <v>1</v>
@@ -7254,6 +7391,9 @@
       </c>
       <c r="W84" t="n">
         <v>-1</v>
+      </c>
+      <c r="X84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -7336,6 +7476,9 @@
       <c r="W85" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7374,10 +7517,8 @@
       <c r="L86" t="n">
         <v>2</v>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M86" t="n">
+        <v>4</v>
       </c>
       <c r="N86" t="n">
         <v>2</v>
@@ -7416,6 +7557,9 @@
       </c>
       <c r="W86" t="n">
         <v>1</v>
+      </c>
+      <c r="X86" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -7455,10 +7599,8 @@
       <c r="L87" t="n">
         <v>2</v>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M87" t="n">
+        <v>4</v>
       </c>
       <c r="N87" t="n">
         <v>3</v>
@@ -7496,6 +7638,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W87" t="n">
+        <v>1</v>
+      </c>
+      <c r="X87" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7536,10 +7681,8 @@
       <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M88" t="n">
+        <v>4</v>
       </c>
       <c r="N88" t="n">
         <v>2</v>
@@ -7577,6 +7720,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W88" t="n">
+        <v>1</v>
+      </c>
+      <c r="X88" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7660,6 +7806,9 @@
       <c r="W89" t="n">
         <v>-1</v>
       </c>
+      <c r="X89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7698,10 +7847,8 @@
       <c r="L90" t="n">
         <v>4</v>
       </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M90" t="n">
+        <v>4</v>
       </c>
       <c r="N90" t="n">
         <v>2</v>
@@ -7740,6 +7887,9 @@
       </c>
       <c r="W90" t="n">
         <v>-1</v>
+      </c>
+      <c r="X90" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7779,10 +7929,8 @@
       <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M91" t="n">
+        <v>4</v>
       </c>
       <c r="N91" t="n">
         <v>2</v>
@@ -7821,6 +7969,9 @@
       </c>
       <c r="W91" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X91" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7903,6 +8054,9 @@
       <c r="W92" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7984,6 +8138,9 @@
       <c r="W93" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8022,10 +8179,8 @@
       <c r="L94" t="n">
         <v>4</v>
       </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M94" t="n">
+        <v>4</v>
       </c>
       <c r="N94" t="n">
         <v>2</v>
@@ -8064,6 +8219,9 @@
       </c>
       <c r="W94" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X94" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -8103,10 +8261,8 @@
       <c r="L95" t="n">
         <v>5</v>
       </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M95" t="n">
+        <v>4</v>
       </c>
       <c r="N95" t="n">
         <v>2</v>
@@ -8145,6 +8301,9 @@
       </c>
       <c r="W95" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X95" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -8184,10 +8343,8 @@
       <c r="L96" t="n">
         <v>3</v>
       </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M96" t="n">
+        <v>5</v>
       </c>
       <c r="N96" t="n">
         <v>2</v>
@@ -8225,6 +8382,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W96" t="n">
+        <v>1</v>
+      </c>
+      <c r="X96" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8308,6 +8468,9 @@
       <c r="W97" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8346,10 +8509,8 @@
       <c r="L98" t="n">
         <v>4</v>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M98" t="n">
+        <v>4</v>
       </c>
       <c r="N98" t="n">
         <v>2</v>
@@ -8389,6 +8550,9 @@
       <c r="W98" t="n">
         <v>-1</v>
       </c>
+      <c r="X98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8427,10 +8591,8 @@
       <c r="L99" t="n">
         <v>5</v>
       </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M99" t="n">
+        <v>5</v>
       </c>
       <c r="N99" t="n">
         <v>2</v>
@@ -8469,6 +8631,9 @@
       </c>
       <c r="W99" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X99" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -8508,10 +8673,8 @@
       <c r="L100" t="n">
         <v>4</v>
       </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M100" t="n">
+        <v>5</v>
       </c>
       <c r="N100" t="n">
         <v>2</v>
@@ -8550,6 +8713,9 @@
       </c>
       <c r="W100" t="n">
         <v>-1</v>
+      </c>
+      <c r="X100" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -8589,10 +8755,8 @@
       <c r="L101" t="n">
         <v>5</v>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M101" t="n">
+        <v>3</v>
       </c>
       <c r="N101" t="n">
         <v>2</v>
@@ -8631,6 +8795,9 @@
       </c>
       <c r="W101" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X101" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -8713,6 +8880,9 @@
       <c r="W102" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X102" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8794,6 +8964,9 @@
       <c r="W103" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X103" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8832,10 +9005,8 @@
       <c r="L104" t="n">
         <v>5</v>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M104" t="n">
+        <v>5</v>
       </c>
       <c r="N104" t="n">
         <v>2</v>
@@ -8874,6 +9045,9 @@
       </c>
       <c r="W104" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X104" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -8913,10 +9087,8 @@
       <c r="L105" t="n">
         <v>4</v>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M105" t="n">
+        <v>4</v>
       </c>
       <c r="N105" t="n">
         <v>2</v>
@@ -8955,6 +9127,9 @@
       </c>
       <c r="W105" t="n">
         <v>1</v>
+      </c>
+      <c r="X105" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -8994,10 +9169,8 @@
       <c r="L106" t="n">
         <v>4</v>
       </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M106" t="n">
+        <v>4</v>
       </c>
       <c r="N106" t="n">
         <v>2</v>
@@ -9036,6 +9209,9 @@
       </c>
       <c r="W106" t="n">
         <v>-1</v>
+      </c>
+      <c r="X106" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -9075,10 +9251,8 @@
       <c r="L107" t="n">
         <v>4</v>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M107" t="n">
+        <v>4</v>
       </c>
       <c r="N107" t="n">
         <v>2</v>
@@ -9117,6 +9291,9 @@
       </c>
       <c r="W107" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X107" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -9156,10 +9333,8 @@
       <c r="L108" t="n">
         <v>4</v>
       </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M108" t="n">
+        <v>4</v>
       </c>
       <c r="N108" t="n">
         <v>2</v>
@@ -9198,6 +9373,9 @@
       </c>
       <c r="W108" t="n">
         <v>-1</v>
+      </c>
+      <c r="X108" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -9237,10 +9415,8 @@
       <c r="L109" t="n">
         <v>2</v>
       </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M109" t="n">
+        <v>4</v>
       </c>
       <c r="N109" t="n">
         <v>2</v>
@@ -9279,6 +9455,9 @@
       </c>
       <c r="W109" t="n">
         <v>-1</v>
+      </c>
+      <c r="X109" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -9361,6 +9540,9 @@
       <c r="W110" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X110" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9399,10 +9581,8 @@
       <c r="L111" t="n">
         <v>5</v>
       </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M111" t="n">
+        <v>4</v>
       </c>
       <c r="N111" t="n">
         <v>2</v>
@@ -9441,6 +9621,9 @@
       </c>
       <c r="W111" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X111" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -9523,6 +9706,9 @@
       <c r="W112" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X112" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9561,10 +9747,8 @@
       <c r="L113" t="n">
         <v>4</v>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M113" t="n">
+        <v>4</v>
       </c>
       <c r="N113" t="n">
         <v>2</v>
@@ -9602,6 +9786,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W113" t="n">
+        <v>1</v>
+      </c>
+      <c r="X113" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9642,10 +9829,8 @@
       <c r="L114" t="n">
         <v>3</v>
       </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M114" t="n">
+        <v>4</v>
       </c>
       <c r="N114" t="n">
         <v>2</v>
@@ -9684,6 +9869,9 @@
       </c>
       <c r="W114" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X114" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -9723,10 +9911,8 @@
       <c r="L115" t="n">
         <v>2</v>
       </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M115" t="n">
+        <v>5</v>
       </c>
       <c r="N115" t="n">
         <v>2</v>
@@ -9765,6 +9951,9 @@
       </c>
       <c r="W115" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X115" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -9804,10 +9993,8 @@
       <c r="L116" t="n">
         <v>1</v>
       </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M116" t="n">
+        <v>5</v>
       </c>
       <c r="N116" t="n">
         <v>2</v>
@@ -9845,6 +10032,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W116" t="n">
+        <v>1</v>
+      </c>
+      <c r="X116" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9928,6 +10118,9 @@
       <c r="W117" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X117" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9966,10 +10159,8 @@
       <c r="L118" t="n">
         <v>5</v>
       </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M118" t="n">
+        <v>4</v>
       </c>
       <c r="N118" t="n">
         <v>2</v>
@@ -10008,6 +10199,9 @@
       </c>
       <c r="W118" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X118" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -10047,10 +10241,8 @@
       <c r="L119" t="n">
         <v>2</v>
       </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M119" t="n">
+        <v>4</v>
       </c>
       <c r="N119" t="n">
         <v>2</v>
@@ -10089,6 +10281,9 @@
       </c>
       <c r="W119" t="n">
         <v>1</v>
+      </c>
+      <c r="X119" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -10171,6 +10366,9 @@
       <c r="W120" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -10209,10 +10407,8 @@
       <c r="L121" t="n">
         <v>5</v>
       </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M121" t="n">
+        <v>4</v>
       </c>
       <c r="N121" t="n">
         <v>2</v>
@@ -10251,6 +10447,9 @@
       </c>
       <c r="W121" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X121" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -10290,10 +10489,8 @@
       <c r="L122" t="n">
         <v>4</v>
       </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M122" t="n">
+        <v>5</v>
       </c>
       <c r="N122" t="n">
         <v>1</v>
@@ -10332,6 +10529,9 @@
       </c>
       <c r="W122" t="n">
         <v>-1</v>
+      </c>
+      <c r="X122" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -10371,10 +10571,8 @@
       <c r="L123" t="n">
         <v>3</v>
       </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M123" t="n">
+        <v>4</v>
       </c>
       <c r="N123" t="n">
         <v>2</v>
@@ -10413,6 +10611,9 @@
       </c>
       <c r="W123" t="n">
         <v>-1</v>
+      </c>
+      <c r="X123" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -10495,6 +10696,9 @@
       <c r="W124" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X124" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -10576,6 +10780,9 @@
       <c r="W125" t="n">
         <v>-1</v>
       </c>
+      <c r="X125" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -10614,10 +10821,8 @@
       <c r="L126" t="n">
         <v>5</v>
       </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M126" t="n">
+        <v>4</v>
       </c>
       <c r="N126" t="n">
         <v>2</v>
@@ -10656,6 +10861,9 @@
       </c>
       <c r="W126" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X126" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -10695,10 +10903,8 @@
       <c r="L127" t="n">
         <v>3</v>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M127" t="n">
+        <v>1</v>
       </c>
       <c r="N127" t="n">
         <v>0</v>
@@ -10737,6 +10943,9 @@
       </c>
       <c r="W127" t="n">
         <v>-1</v>
+      </c>
+      <c r="X127" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -10819,6 +11028,9 @@
       <c r="W128" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X128" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10857,10 +11069,8 @@
       <c r="L129" t="n">
         <v>2</v>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M129" t="n">
+        <v>4</v>
       </c>
       <c r="N129" t="n">
         <v>2</v>
@@ -10899,6 +11109,9 @@
       </c>
       <c r="W129" t="n">
         <v>1</v>
+      </c>
+      <c r="X129" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -10938,10 +11151,8 @@
       <c r="L130" t="n">
         <v>5</v>
       </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M130" t="n">
+        <v>4</v>
       </c>
       <c r="N130" t="n">
         <v>2</v>
@@ -10980,6 +11191,9 @@
       </c>
       <c r="W130" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X130" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -11062,6 +11276,9 @@
       <c r="W131" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X131" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -11100,10 +11317,8 @@
       <c r="L132" t="n">
         <v>4</v>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M132" t="n">
+        <v>4</v>
       </c>
       <c r="N132" t="n">
         <v>2</v>
@@ -11142,6 +11357,9 @@
       </c>
       <c r="W132" t="n">
         <v>-1</v>
+      </c>
+      <c r="X132" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -11181,10 +11399,8 @@
       <c r="L133" t="n">
         <v>5</v>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M133" t="n">
+        <v>1</v>
       </c>
       <c r="N133" t="n">
         <v>2</v>
@@ -11223,6 +11439,9 @@
       </c>
       <c r="W133" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X133" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -11305,6 +11524,9 @@
       <c r="W134" t="n">
         <v>1</v>
       </c>
+      <c r="X134" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11386,6 +11608,9 @@
       <c r="W135" t="n">
         <v>-1</v>
       </c>
+      <c r="X135" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -11424,10 +11649,8 @@
       <c r="L136" t="n">
         <v>3</v>
       </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M136" t="n">
+        <v>1</v>
       </c>
       <c r="N136" t="n">
         <v>2</v>
@@ -11466,6 +11689,9 @@
       </c>
       <c r="W136" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X136" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -11505,10 +11731,8 @@
       <c r="L137" t="n">
         <v>4</v>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M137" t="n">
+        <v>4</v>
       </c>
       <c r="N137" t="n">
         <v>2</v>
@@ -11547,6 +11771,9 @@
       </c>
       <c r="W137" t="n">
         <v>1</v>
+      </c>
+      <c r="X137" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -11586,10 +11813,8 @@
       <c r="L138" t="n">
         <v>4</v>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M138" t="n">
+        <v>3</v>
       </c>
       <c r="N138" t="n">
         <v>2</v>
@@ -11628,6 +11853,9 @@
       </c>
       <c r="W138" t="n">
         <v>-1</v>
+      </c>
+      <c r="X138" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -11667,10 +11895,8 @@
       <c r="L139" t="n">
         <v>2</v>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M139" t="n">
+        <v>4</v>
       </c>
       <c r="N139" t="n">
         <v>2</v>
@@ -11709,6 +11935,9 @@
       </c>
       <c r="W139" t="n">
         <v>1</v>
+      </c>
+      <c r="X139" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -11791,6 +12020,9 @@
       <c r="W140" t="n">
         <v>-1</v>
       </c>
+      <c r="X140" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11829,10 +12061,8 @@
       <c r="L141" t="n">
         <v>5</v>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M141" t="n">
+        <v>4</v>
       </c>
       <c r="N141" t="n">
         <v>1</v>
@@ -11871,6 +12101,9 @@
       </c>
       <c r="W141" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X141" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -11910,10 +12143,8 @@
       <c r="L142" t="n">
         <v>5</v>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M142" t="n">
+        <v>4</v>
       </c>
       <c r="N142" t="n">
         <v>2</v>
@@ -11952,6 +12183,9 @@
       </c>
       <c r="W142" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X142" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -11991,10 +12225,8 @@
       <c r="L143" t="n">
         <v>4</v>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M143" t="n">
+        <v>1</v>
       </c>
       <c r="N143" t="n">
         <v>0</v>
@@ -12033,6 +12265,9 @@
       </c>
       <c r="W143" t="n">
         <v>-1</v>
+      </c>
+      <c r="X143" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -12115,6 +12350,9 @@
       <c r="W144" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X144" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -12196,6 +12434,9 @@
       <c r="W145" t="n">
         <v>1</v>
       </c>
+      <c r="X145" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -12277,6 +12518,9 @@
       <c r="W146" t="n">
         <v>-1</v>
       </c>
+      <c r="X146" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -12315,10 +12559,8 @@
       <c r="L147" t="n">
         <v>5</v>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M147" t="n">
+        <v>4</v>
       </c>
       <c r="N147" t="n">
         <v>1</v>
@@ -12357,6 +12599,9 @@
       </c>
       <c r="W147" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X147" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -12396,10 +12641,8 @@
       <c r="L148" t="n">
         <v>4</v>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M148" t="n">
+        <v>1</v>
       </c>
       <c r="N148" t="n">
         <v>2</v>
@@ -12438,6 +12681,9 @@
       </c>
       <c r="W148" t="n">
         <v>-1</v>
+      </c>
+      <c r="X148" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -12520,6 +12766,9 @@
       <c r="W149" t="n">
         <v>1</v>
       </c>
+      <c r="X149" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -12558,10 +12807,8 @@
       <c r="L150" t="n">
         <v>3</v>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M150" t="n">
+        <v>3</v>
       </c>
       <c r="N150" t="n">
         <v>2</v>
@@ -12600,6 +12847,9 @@
       </c>
       <c r="W150" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X150" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -12639,10 +12889,8 @@
       <c r="L151" t="n">
         <v>5</v>
       </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M151" t="n">
+        <v>4</v>
       </c>
       <c r="N151" t="n">
         <v>1</v>
@@ -12681,6 +12929,9 @@
       </c>
       <c r="W151" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X151" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -12763,6 +13014,9 @@
       <c r="W152" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X152" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -12844,6 +13098,9 @@
       <c r="W153" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X153" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -12882,10 +13139,8 @@
       <c r="L154" t="n">
         <v>4</v>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M154" t="n">
+        <v>4</v>
       </c>
       <c r="N154" t="n">
         <v>2</v>
@@ -12924,6 +13179,9 @@
       </c>
       <c r="W154" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X154" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -12963,10 +13221,8 @@
       <c r="L155" t="n">
         <v>4</v>
       </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="M155" t="n">
+        <v>2</v>
       </c>
       <c r="N155" t="n">
         <v>2</v>
@@ -13005,6 +13261,9 @@
       </c>
       <c r="W155" t="n">
         <v>-1</v>
+      </c>
+      <c r="X155" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -13087,6 +13346,9 @@
       <c r="W156" t="n">
         <v>-1</v>
       </c>
+      <c r="X156" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -13125,10 +13387,8 @@
       <c r="L157" t="n">
         <v>5</v>
       </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M157" t="n">
+        <v>4</v>
       </c>
       <c r="N157" t="n">
         <v>2</v>
@@ -13167,6 +13427,9 @@
       </c>
       <c r="W157" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X157" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -13206,10 +13469,8 @@
       <c r="L158" t="n">
         <v>4</v>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M158" t="n">
+        <v>5</v>
       </c>
       <c r="N158" t="n">
         <v>2</v>
@@ -13248,6 +13509,9 @@
       </c>
       <c r="W158" t="n">
         <v>-1</v>
+      </c>
+      <c r="X158" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -13287,10 +13551,8 @@
       <c r="L159" t="n">
         <v>3</v>
       </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M159" t="n">
+        <v>4</v>
       </c>
       <c r="N159" t="n">
         <v>2</v>
@@ -13329,6 +13591,9 @@
       </c>
       <c r="W159" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X159" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -13411,6 +13676,9 @@
       <c r="W160" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X160" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -13492,6 +13760,9 @@
       <c r="W161" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X161" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -13530,10 +13801,8 @@
       <c r="L162" t="n">
         <v>5</v>
       </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M162" t="n">
+        <v>1</v>
       </c>
       <c r="N162" t="n">
         <v>1</v>
@@ -13572,6 +13841,9 @@
       </c>
       <c r="W162" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X162" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -13611,10 +13883,8 @@
       <c r="L163" t="n">
         <v>4</v>
       </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M163" t="n">
+        <v>4</v>
       </c>
       <c r="N163" t="n">
         <v>2</v>
@@ -13653,6 +13923,9 @@
       </c>
       <c r="W163" t="n">
         <v>-1</v>
+      </c>
+      <c r="X163" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -13692,10 +13965,8 @@
       <c r="L164" t="n">
         <v>4</v>
       </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M164" t="n">
+        <v>4</v>
       </c>
       <c r="N164" t="n">
         <v>2</v>
@@ -13734,6 +14005,9 @@
       </c>
       <c r="W164" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X164" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -13773,10 +14047,8 @@
       <c r="L165" t="n">
         <v>2</v>
       </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M165" t="n">
+        <v>4</v>
       </c>
       <c r="N165" t="n">
         <v>2</v>
@@ -13815,6 +14087,9 @@
       </c>
       <c r="W165" t="n">
         <v>1</v>
+      </c>
+      <c r="X165" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -13854,10 +14129,8 @@
       <c r="L166" t="n">
         <v>5</v>
       </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M166" t="n">
+        <v>4</v>
       </c>
       <c r="N166" t="n">
         <v>1</v>
@@ -13896,6 +14169,9 @@
       </c>
       <c r="W166" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X166" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -13935,10 +14211,8 @@
       <c r="L167" t="n">
         <v>2</v>
       </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M167" t="n">
+        <v>4</v>
       </c>
       <c r="N167" t="n">
         <v>0</v>
@@ -13977,6 +14251,9 @@
       </c>
       <c r="W167" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X167" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -14016,10 +14293,8 @@
       <c r="L168" t="n">
         <v>5</v>
       </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M168" t="n">
+        <v>1</v>
       </c>
       <c r="N168" t="n">
         <v>2</v>
@@ -14058,6 +14333,9 @@
       </c>
       <c r="W168" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X168" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -14140,6 +14418,9 @@
       <c r="W169" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X169" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -14178,10 +14459,8 @@
       <c r="L170" t="n">
         <v>4</v>
       </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M170" t="n">
+        <v>4</v>
       </c>
       <c r="N170" t="n">
         <v>2</v>
@@ -14220,6 +14499,9 @@
       </c>
       <c r="W170" t="n">
         <v>-1</v>
+      </c>
+      <c r="X170" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -14259,10 +14541,8 @@
       <c r="L171" t="n">
         <v>4</v>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M171" t="n">
+        <v>4</v>
       </c>
       <c r="N171" t="n">
         <v>2</v>
@@ -14301,6 +14581,9 @@
       </c>
       <c r="W171" t="n">
         <v>-1</v>
+      </c>
+      <c r="X171" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -14340,10 +14623,8 @@
       <c r="L172" t="n">
         <v>4</v>
       </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M172" t="n">
+        <v>4</v>
       </c>
       <c r="N172" t="n">
         <v>0</v>
@@ -14382,6 +14663,9 @@
       </c>
       <c r="W172" t="n">
         <v>-1</v>
+      </c>
+      <c r="X172" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -14464,6 +14748,9 @@
       <c r="W173" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X173" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -14502,10 +14789,8 @@
       <c r="L174" t="n">
         <v>4</v>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M174" t="n">
+        <v>4</v>
       </c>
       <c r="N174" t="n">
         <v>2</v>
@@ -14543,6 +14828,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W174" t="n">
+        <v>1</v>
+      </c>
+      <c r="X174" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14626,6 +14914,9 @@
       <c r="W175" t="n">
         <v>-1</v>
       </c>
+      <c r="X175" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -14707,6 +14998,9 @@
       <c r="W176" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X176" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -14788,6 +15082,9 @@
       <c r="W177" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X177" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -14826,10 +15123,8 @@
       <c r="L178" t="n">
         <v>2</v>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M178" t="n">
+        <v>5</v>
       </c>
       <c r="N178" t="n">
         <v>2</v>
@@ -14868,6 +15163,9 @@
       </c>
       <c r="W178" t="n">
         <v>-1</v>
+      </c>
+      <c r="X178" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -14907,10 +15205,8 @@
       <c r="L179" t="n">
         <v>4</v>
       </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M179" t="n">
+        <v>4</v>
       </c>
       <c r="N179" t="n">
         <v>2</v>
@@ -14949,6 +15245,9 @@
       </c>
       <c r="W179" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X179" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -15031,6 +15330,9 @@
       <c r="W180" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X180" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -15069,10 +15371,8 @@
       <c r="L181" t="n">
         <v>4</v>
       </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M181" t="n">
+        <v>5</v>
       </c>
       <c r="N181" t="n">
         <v>2</v>
@@ -15111,6 +15411,9 @@
       </c>
       <c r="W181" t="n">
         <v>-1</v>
+      </c>
+      <c r="X181" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -15150,10 +15453,8 @@
       <c r="L182" t="n">
         <v>5</v>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M182" t="n">
+        <v>5</v>
       </c>
       <c r="N182" t="n">
         <v>2</v>
@@ -15192,6 +15493,9 @@
       </c>
       <c r="W182" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X182" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -15231,10 +15535,8 @@
       <c r="L183" t="n">
         <v>3</v>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M183" t="n">
+        <v>4</v>
       </c>
       <c r="N183" t="n">
         <v>2</v>
@@ -15273,6 +15575,9 @@
       </c>
       <c r="W183" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X183" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -15312,10 +15617,8 @@
       <c r="L184" t="n">
         <v>4</v>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M184" t="n">
+        <v>5</v>
       </c>
       <c r="N184" t="n">
         <v>1</v>
@@ -15354,6 +15657,9 @@
       </c>
       <c r="W184" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X184" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -15436,6 +15742,9 @@
       <c r="W185" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X185" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -15517,6 +15826,9 @@
       <c r="W186" t="n">
         <v>1</v>
       </c>
+      <c r="X186" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -15598,6 +15910,9 @@
       <c r="W187" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X187" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -15636,10 +15951,8 @@
       <c r="L188" t="n">
         <v>2</v>
       </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M188" t="n">
+        <v>4</v>
       </c>
       <c r="N188" t="n">
         <v>3</v>
@@ -15677,6 +15990,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W188" t="n">
+        <v>1</v>
+      </c>
+      <c r="X188" t="b">
         <v>1</v>
       </c>
     </row>
@@ -15760,6 +16076,9 @@
       <c r="W189" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X189" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -15798,10 +16117,8 @@
       <c r="L190" t="n">
         <v>2</v>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M190" t="n">
+        <v>4</v>
       </c>
       <c r="N190" t="n">
         <v>3</v>
@@ -15840,6 +16157,9 @@
       </c>
       <c r="W190" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X190" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -15879,10 +16199,8 @@
       <c r="L191" t="n">
         <v>3</v>
       </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M191" t="n">
+        <v>4</v>
       </c>
       <c r="N191" t="n">
         <v>2</v>
@@ -15921,6 +16239,9 @@
       </c>
       <c r="W191" t="n">
         <v>-1</v>
+      </c>
+      <c r="X191" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -15960,10 +16281,8 @@
       <c r="L192" t="n">
         <v>5</v>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M192" t="n">
+        <v>1</v>
       </c>
       <c r="N192" t="n">
         <v>2</v>
@@ -16002,6 +16321,9 @@
       </c>
       <c r="W192" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X192" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -16041,10 +16363,8 @@
       <c r="L193" t="n">
         <v>4</v>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M193" t="n">
+        <v>4</v>
       </c>
       <c r="N193" t="n">
         <v>2</v>
@@ -16083,6 +16403,9 @@
       </c>
       <c r="W193" t="n">
         <v>-1</v>
+      </c>
+      <c r="X193" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -16165,6 +16488,9 @@
       <c r="W194" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X194" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -16203,10 +16529,8 @@
       <c r="L195" t="n">
         <v>3</v>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M195" t="n">
+        <v>4</v>
       </c>
       <c r="N195" t="n">
         <v>2</v>
@@ -16245,6 +16569,9 @@
       </c>
       <c r="W195" t="n">
         <v>-1</v>
+      </c>
+      <c r="X195" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -16284,10 +16611,8 @@
       <c r="L196" t="n">
         <v>5</v>
       </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M196" t="n">
+        <v>4</v>
       </c>
       <c r="N196" t="n">
         <v>2</v>
@@ -16326,6 +16651,9 @@
       </c>
       <c r="W196" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X196" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -16408,6 +16736,9 @@
       <c r="W197" t="n">
         <v>-1</v>
       </c>
+      <c r="X197" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -16446,10 +16777,8 @@
       <c r="L198" t="n">
         <v>2</v>
       </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M198" t="n">
+        <v>4</v>
       </c>
       <c r="N198" t="n">
         <v>2</v>
@@ -16488,6 +16817,9 @@
       </c>
       <c r="W198" t="n">
         <v>-1</v>
+      </c>
+      <c r="X198" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -16570,6 +16902,9 @@
       <c r="W199" t="n">
         <v>-1</v>
       </c>
+      <c r="X199" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -16608,10 +16943,8 @@
       <c r="L200" t="n">
         <v>4</v>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M200" t="n">
+        <v>4</v>
       </c>
       <c r="N200" t="n">
         <v>2</v>
@@ -16650,6 +16983,9 @@
       </c>
       <c r="W200" t="n">
         <v>-1</v>
+      </c>
+      <c r="X200" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -16689,10 +17025,8 @@
       <c r="L201" t="n">
         <v>4</v>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M201" t="n">
+        <v>4</v>
       </c>
       <c r="N201" t="n">
         <v>2</v>
@@ -16731,6 +17065,9 @@
       </c>
       <c r="W201" t="n">
         <v>-1</v>
+      </c>
+      <c r="X201" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -16770,10 +17107,8 @@
       <c r="L202" t="n">
         <v>2</v>
       </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M202" t="n">
+        <v>4</v>
       </c>
       <c r="N202" t="n">
         <v>1</v>
@@ -16812,6 +17147,9 @@
       </c>
       <c r="W202" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X202" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -16851,10 +17189,8 @@
       <c r="L203" t="n">
         <v>5</v>
       </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M203" t="n">
+        <v>1</v>
       </c>
       <c r="N203" t="n">
         <v>1</v>
@@ -16893,6 +17229,9 @@
       </c>
       <c r="W203" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X203" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -16975,6 +17314,9 @@
       <c r="W204" t="n">
         <v>-1</v>
       </c>
+      <c r="X204" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -17013,10 +17355,8 @@
       <c r="L205" t="n">
         <v>3</v>
       </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M205" t="n">
+        <v>4</v>
       </c>
       <c r="N205" t="n">
         <v>2</v>
@@ -17054,6 +17394,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W205" t="n">
+        <v>1</v>
+      </c>
+      <c r="X205" t="b">
         <v>1</v>
       </c>
     </row>
@@ -17137,6 +17480,9 @@
       <c r="W206" t="n">
         <v>-1</v>
       </c>
+      <c r="X206" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -17175,10 +17521,8 @@
       <c r="L207" t="n">
         <v>4</v>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M207" t="n">
+        <v>4</v>
       </c>
       <c r="N207" t="n">
         <v>2</v>
@@ -17217,6 +17561,9 @@
       </c>
       <c r="W207" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X207" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -17299,6 +17646,9 @@
       <c r="W208" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X208" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -17337,10 +17687,8 @@
       <c r="L209" t="n">
         <v>2</v>
       </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M209" t="n">
+        <v>4</v>
       </c>
       <c r="N209" t="n">
         <v>3</v>
@@ -17379,6 +17727,9 @@
       </c>
       <c r="W209" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X209" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -17461,6 +17812,9 @@
       <c r="W210" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X210" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -17499,10 +17853,8 @@
       <c r="L211" t="n">
         <v>4</v>
       </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M211" t="n">
+        <v>4</v>
       </c>
       <c r="N211" t="n">
         <v>2</v>
@@ -17541,6 +17893,9 @@
       </c>
       <c r="W211" t="n">
         <v>1</v>
+      </c>
+      <c r="X211" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -17580,10 +17935,8 @@
       <c r="L212" t="n">
         <v>2</v>
       </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M212" t="n">
+        <v>4</v>
       </c>
       <c r="N212" t="n">
         <v>2</v>
@@ -17622,6 +17975,9 @@
       </c>
       <c r="W212" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X212" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -17661,10 +18017,8 @@
       <c r="L213" t="n">
         <v>4</v>
       </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M213" t="n">
+        <v>4</v>
       </c>
       <c r="N213" t="n">
         <v>2</v>
@@ -17703,6 +18057,9 @@
       </c>
       <c r="W213" t="n">
         <v>-1</v>
+      </c>
+      <c r="X213" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -17742,10 +18099,8 @@
       <c r="L214" t="n">
         <v>4</v>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M214" t="n">
+        <v>5</v>
       </c>
       <c r="N214" t="n">
         <v>2</v>
@@ -17784,6 +18139,9 @@
       </c>
       <c r="W214" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X214" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -17866,6 +18224,9 @@
       <c r="W215" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X215" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -17947,6 +18308,9 @@
       <c r="W216" t="n">
         <v>-1</v>
       </c>
+      <c r="X216" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -17985,10 +18349,8 @@
       <c r="L217" t="n">
         <v>5</v>
       </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M217" t="n">
+        <v>4</v>
       </c>
       <c r="N217" t="n">
         <v>2</v>
@@ -18027,6 +18389,9 @@
       </c>
       <c r="W217" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X217" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -18109,6 +18474,9 @@
       <c r="W218" t="n">
         <v>1</v>
       </c>
+      <c r="X218" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -18147,10 +18515,8 @@
       <c r="L219" t="n">
         <v>5</v>
       </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M219" t="n">
+        <v>5</v>
       </c>
       <c r="N219" t="n">
         <v>2</v>
@@ -18189,6 +18555,9 @@
       </c>
       <c r="W219" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X219" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -18228,10 +18597,8 @@
       <c r="L220" t="n">
         <v>5</v>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M220" t="n">
+        <v>4</v>
       </c>
       <c r="N220" t="n">
         <v>2</v>
@@ -18270,6 +18637,9 @@
       </c>
       <c r="W220" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X220" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -18352,6 +18722,9 @@
       <c r="W221" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X221" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -18390,10 +18763,8 @@
       <c r="L222" t="n">
         <v>2</v>
       </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M222" t="n">
+        <v>4</v>
       </c>
       <c r="N222" t="n">
         <v>3</v>
@@ -18431,6 +18802,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W222" t="n">
+        <v>1</v>
+      </c>
+      <c r="X222" t="b">
         <v>1</v>
       </c>
     </row>
@@ -18514,6 +18888,9 @@
       <c r="W223" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X223" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -18552,10 +18929,8 @@
       <c r="L224" t="n">
         <v>3</v>
       </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M224" t="n">
+        <v>5</v>
       </c>
       <c r="N224" t="n">
         <v>2</v>
@@ -18594,6 +18969,9 @@
       </c>
       <c r="W224" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X224" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -18633,10 +19011,8 @@
       <c r="L225" t="n">
         <v>4</v>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M225" t="n">
+        <v>4</v>
       </c>
       <c r="N225" t="n">
         <v>2</v>
@@ -18675,6 +19051,9 @@
       </c>
       <c r="W225" t="n">
         <v>1</v>
+      </c>
+      <c r="X225" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -18757,6 +19136,9 @@
       <c r="W226" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X226" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -18795,10 +19177,8 @@
       <c r="L227" t="n">
         <v>4</v>
       </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M227" t="n">
+        <v>4</v>
       </c>
       <c r="N227" t="n">
         <v>2</v>
@@ -18837,6 +19217,9 @@
       </c>
       <c r="W227" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X227" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -18876,10 +19259,8 @@
       <c r="L228" t="n">
         <v>4</v>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M228" t="n">
+        <v>4</v>
       </c>
       <c r="N228" t="n">
         <v>2</v>
@@ -18918,6 +19299,9 @@
       </c>
       <c r="W228" t="n">
         <v>-1</v>
+      </c>
+      <c r="X228" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -18957,10 +19341,8 @@
       <c r="L229" t="n">
         <v>3</v>
       </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M229" t="n">
+        <v>5</v>
       </c>
       <c r="N229" t="n">
         <v>2</v>
@@ -18999,6 +19381,9 @@
       </c>
       <c r="W229" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X229" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -19081,6 +19466,9 @@
       <c r="W230" t="n">
         <v>-1</v>
       </c>
+      <c r="X230" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -19162,6 +19550,9 @@
       <c r="W231" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X231" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -19243,6 +19634,9 @@
       <c r="W232" t="n">
         <v>1</v>
       </c>
+      <c r="X232" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -19281,10 +19675,8 @@
       <c r="L233" t="n">
         <v>2</v>
       </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M233" t="n">
+        <v>4</v>
       </c>
       <c r="N233" t="n">
         <v>2</v>
@@ -19323,6 +19715,9 @@
       </c>
       <c r="W233" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X233" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -19405,6 +19800,9 @@
       <c r="W234" t="n">
         <v>-1</v>
       </c>
+      <c r="X234" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -19486,6 +19884,9 @@
       <c r="W235" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X235" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -19567,6 +19968,9 @@
       <c r="W236" t="n">
         <v>-1</v>
       </c>
+      <c r="X236" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -19648,6 +20052,9 @@
       <c r="W237" t="n">
         <v>-1</v>
       </c>
+      <c r="X237" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -19686,10 +20093,8 @@
       <c r="L238" t="n">
         <v>4</v>
       </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M238" t="n">
+        <v>4</v>
       </c>
       <c r="N238" t="n">
         <v>2</v>
@@ -19728,6 +20133,9 @@
       </c>
       <c r="W238" t="n">
         <v>-1</v>
+      </c>
+      <c r="X238" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -19767,10 +20175,8 @@
       <c r="L239" t="n">
         <v>5</v>
       </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M239" t="n">
+        <v>4</v>
       </c>
       <c r="N239" t="n">
         <v>2</v>
@@ -19809,6 +20215,9 @@
       </c>
       <c r="W239" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X239" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -19891,6 +20300,9 @@
       <c r="W240" t="n">
         <v>-1</v>
       </c>
+      <c r="X240" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -19929,10 +20341,8 @@
       <c r="L241" t="n">
         <v>4</v>
       </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M241" t="n">
+        <v>4</v>
       </c>
       <c r="N241" t="n">
         <v>2</v>
@@ -19971,6 +20381,9 @@
       </c>
       <c r="W241" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X241" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -20010,10 +20423,8 @@
       <c r="L242" t="n">
         <v>4</v>
       </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M242" t="n">
+        <v>4</v>
       </c>
       <c r="N242" t="n">
         <v>1</v>
@@ -20052,6 +20463,9 @@
       </c>
       <c r="W242" t="n">
         <v>-1</v>
+      </c>
+      <c r="X242" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -20091,10 +20505,8 @@
       <c r="L243" t="n">
         <v>4</v>
       </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M243" t="n">
+        <v>3</v>
       </c>
       <c r="N243" t="n">
         <v>0</v>
@@ -20133,6 +20545,9 @@
       </c>
       <c r="W243" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X243" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -20172,10 +20587,8 @@
       <c r="L244" t="n">
         <v>4</v>
       </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M244" t="n">
+        <v>1</v>
       </c>
       <c r="N244" t="n">
         <v>1</v>
@@ -20214,6 +20627,9 @@
       </c>
       <c r="W244" t="n">
         <v>-1</v>
+      </c>
+      <c r="X244" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -20296,6 +20712,9 @@
       <c r="W245" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X245" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -20334,10 +20753,8 @@
       <c r="L246" t="n">
         <v>4</v>
       </c>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M246" t="n">
+        <v>4</v>
       </c>
       <c r="N246" t="n">
         <v>2</v>
@@ -20376,6 +20793,9 @@
       </c>
       <c r="W246" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X246" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -20415,10 +20835,8 @@
       <c r="L247" t="n">
         <v>3</v>
       </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M247" t="n">
+        <v>5</v>
       </c>
       <c r="N247" t="n">
         <v>2</v>
@@ -20456,6 +20874,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W247" t="n">
+        <v>1</v>
+      </c>
+      <c r="X247" t="b">
         <v>1</v>
       </c>
     </row>
@@ -20496,10 +20917,8 @@
       <c r="L248" t="n">
         <v>2</v>
       </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M248" t="n">
+        <v>4</v>
       </c>
       <c r="N248" t="n">
         <v>2</v>
@@ -20538,6 +20957,9 @@
       </c>
       <c r="W248" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X248" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -20620,6 +21042,9 @@
       <c r="W249" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X249" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -20701,6 +21126,9 @@
       <c r="W250" t="n">
         <v>-1</v>
       </c>
+      <c r="X250" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -20739,10 +21167,8 @@
       <c r="L251" t="n">
         <v>4</v>
       </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M251" t="n">
+        <v>4</v>
       </c>
       <c r="N251" t="n">
         <v>2</v>
@@ -20781,6 +21207,9 @@
       </c>
       <c r="W251" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X251" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -20820,10 +21249,8 @@
       <c r="L252" t="n">
         <v>4</v>
       </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M252" t="n">
+        <v>4</v>
       </c>
       <c r="N252" t="n">
         <v>2</v>
@@ -20862,6 +21289,9 @@
       </c>
       <c r="W252" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X252" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -20901,10 +21331,8 @@
       <c r="L253" t="n">
         <v>4</v>
       </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M253" t="n">
+        <v>4</v>
       </c>
       <c r="N253" t="n">
         <v>1</v>
@@ -20943,6 +21371,9 @@
       </c>
       <c r="W253" t="n">
         <v>-1</v>
+      </c>
+      <c r="X253" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -21025,6 +21456,9 @@
       <c r="W254" t="n">
         <v>1</v>
       </c>
+      <c r="X254" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -21106,6 +21540,9 @@
       <c r="W255" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X255" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -21187,6 +21624,9 @@
       <c r="W256" t="n">
         <v>-1</v>
       </c>
+      <c r="X256" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -21225,10 +21665,8 @@
       <c r="L257" t="n">
         <v>4</v>
       </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M257" t="n">
+        <v>5</v>
       </c>
       <c r="N257" t="n">
         <v>1</v>
@@ -21267,6 +21705,9 @@
       </c>
       <c r="W257" t="n">
         <v>-1</v>
+      </c>
+      <c r="X257" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -21306,10 +21747,8 @@
       <c r="L258" t="n">
         <v>4</v>
       </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M258" t="n">
+        <v>5</v>
       </c>
       <c r="N258" t="n">
         <v>2</v>
@@ -21348,6 +21787,9 @@
       </c>
       <c r="W258" t="n">
         <v>-1</v>
+      </c>
+      <c r="X258" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -21387,10 +21829,8 @@
       <c r="L259" t="n">
         <v>5</v>
       </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M259" t="n">
+        <v>4</v>
       </c>
       <c r="N259" t="n">
         <v>0</v>
@@ -21429,6 +21869,9 @@
       </c>
       <c r="W259" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X259" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -21468,10 +21911,8 @@
       <c r="L260" t="n">
         <v>2</v>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M260" t="n">
+        <v>4</v>
       </c>
       <c r="N260" t="n">
         <v>2</v>
@@ -21510,6 +21951,9 @@
       </c>
       <c r="W260" t="n">
         <v>1</v>
+      </c>
+      <c r="X260" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -21549,10 +21993,8 @@
       <c r="L261" t="n">
         <v>5</v>
       </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M261" t="n">
+        <v>1</v>
       </c>
       <c r="N261" t="n">
         <v>2</v>
@@ -21591,6 +22033,9 @@
       </c>
       <c r="W261" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X261" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -21630,10 +22075,8 @@
       <c r="L262" t="n">
         <v>4</v>
       </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M262" t="n">
+        <v>1</v>
       </c>
       <c r="N262" t="n">
         <v>2</v>
@@ -21672,6 +22115,9 @@
       </c>
       <c r="W262" t="n">
         <v>-1</v>
+      </c>
+      <c r="X262" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -21711,10 +22157,8 @@
       <c r="L263" t="n">
         <v>5</v>
       </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M263" t="n">
+        <v>1</v>
       </c>
       <c r="N263" t="n">
         <v>2</v>
@@ -21753,6 +22197,9 @@
       </c>
       <c r="W263" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X263" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -21792,10 +22239,8 @@
       <c r="L264" t="n">
         <v>4</v>
       </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M264" t="n">
+        <v>4</v>
       </c>
       <c r="N264" t="n">
         <v>2</v>
@@ -21834,6 +22279,9 @@
       </c>
       <c r="W264" t="n">
         <v>-1</v>
+      </c>
+      <c r="X264" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -21916,6 +22364,9 @@
       <c r="W265" t="n">
         <v>-1</v>
       </c>
+      <c r="X265" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -21954,10 +22405,8 @@
       <c r="L266" t="n">
         <v>5</v>
       </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M266" t="n">
+        <v>5</v>
       </c>
       <c r="N266" t="n">
         <v>2</v>
@@ -21996,6 +22445,9 @@
       </c>
       <c r="W266" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X266" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -22035,10 +22487,8 @@
       <c r="L267" t="n">
         <v>3</v>
       </c>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M267" t="n">
+        <v>4</v>
       </c>
       <c r="N267" t="n">
         <v>2</v>
@@ -22077,6 +22527,9 @@
       </c>
       <c r="W267" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X267" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -22116,10 +22569,8 @@
       <c r="L268" t="n">
         <v>4</v>
       </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="M268" t="n">
+        <v>2</v>
       </c>
       <c r="N268" t="n">
         <v>2</v>
@@ -22158,6 +22609,9 @@
       </c>
       <c r="W268" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X268" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -22197,10 +22651,8 @@
       <c r="L269" t="n">
         <v>4</v>
       </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M269" t="n">
+        <v>5</v>
       </c>
       <c r="N269" t="n">
         <v>2</v>
@@ -22239,6 +22691,9 @@
       </c>
       <c r="W269" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X269" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -22321,6 +22776,9 @@
       <c r="W270" t="n">
         <v>-1</v>
       </c>
+      <c r="X270" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -22359,10 +22817,8 @@
       <c r="L271" t="n">
         <v>5</v>
       </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M271" t="n">
+        <v>4</v>
       </c>
       <c r="N271" t="n">
         <v>2</v>
@@ -22401,6 +22857,9 @@
       </c>
       <c r="W271" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X271" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -22440,10 +22899,8 @@
       <c r="L272" t="n">
         <v>5</v>
       </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M272" t="n">
+        <v>5</v>
       </c>
       <c r="N272" t="n">
         <v>2</v>
@@ -22482,6 +22939,9 @@
       </c>
       <c r="W272" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X272" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -22521,10 +22981,8 @@
       <c r="L273" t="n">
         <v>4</v>
       </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M273" t="n">
+        <v>4</v>
       </c>
       <c r="N273" t="n">
         <v>2</v>
@@ -22563,6 +23021,9 @@
       </c>
       <c r="W273" t="n">
         <v>-1</v>
+      </c>
+      <c r="X273" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -22645,6 +23106,9 @@
       <c r="W274" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X274" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -22683,10 +23147,8 @@
       <c r="L275" t="n">
         <v>4</v>
       </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M275" t="n">
+        <v>4</v>
       </c>
       <c r="N275" t="n">
         <v>2</v>
@@ -22725,6 +23187,9 @@
       </c>
       <c r="W275" t="n">
         <v>-1</v>
+      </c>
+      <c r="X275" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -22764,10 +23229,8 @@
       <c r="L276" t="n">
         <v>4</v>
       </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M276" t="n">
+        <v>4</v>
       </c>
       <c r="N276" t="n">
         <v>2</v>
@@ -22806,6 +23269,9 @@
       </c>
       <c r="W276" t="n">
         <v>-1</v>
+      </c>
+      <c r="X276" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -22845,10 +23311,8 @@
       <c r="L277" t="n">
         <v>5</v>
       </c>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M277" t="n">
+        <v>1</v>
       </c>
       <c r="N277" t="n">
         <v>2</v>
@@ -22887,6 +23351,9 @@
       </c>
       <c r="W277" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X277" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -22926,10 +23393,8 @@
       <c r="L278" t="n">
         <v>4</v>
       </c>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M278" t="n">
+        <v>4</v>
       </c>
       <c r="N278" t="n">
         <v>2</v>
@@ -22967,6 +23432,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W278" t="n">
+        <v>1</v>
+      </c>
+      <c r="X278" t="b">
         <v>1</v>
       </c>
     </row>
@@ -23007,10 +23475,8 @@
       <c r="L279" t="n">
         <v>4</v>
       </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M279" t="n">
+        <v>1</v>
       </c>
       <c r="N279" t="n">
         <v>1</v>
@@ -23049,6 +23515,9 @@
       </c>
       <c r="W279" t="n">
         <v>-1</v>
+      </c>
+      <c r="X279" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -23088,10 +23557,8 @@
       <c r="L280" t="n">
         <v>4</v>
       </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M280" t="n">
+        <v>4</v>
       </c>
       <c r="N280" t="n">
         <v>2</v>
@@ -23129,6 +23596,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W280" t="n">
+        <v>1</v>
+      </c>
+      <c r="X280" t="b">
         <v>1</v>
       </c>
     </row>
@@ -23169,10 +23639,8 @@
       <c r="L281" t="n">
         <v>4</v>
       </c>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="M281" t="n">
+        <v>2</v>
       </c>
       <c r="N281" t="n">
         <v>2</v>
@@ -23211,6 +23679,9 @@
       </c>
       <c r="W281" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X281" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -23250,10 +23721,8 @@
       <c r="L282" t="n">
         <v>5</v>
       </c>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M282" t="n">
+        <v>1</v>
       </c>
       <c r="N282" t="n">
         <v>2</v>
@@ -23292,6 +23761,9 @@
       </c>
       <c r="W282" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X282" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -23331,10 +23803,8 @@
       <c r="L283" t="n">
         <v>4</v>
       </c>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M283" t="n">
+        <v>4</v>
       </c>
       <c r="N283" t="n">
         <v>2</v>
@@ -23373,6 +23843,9 @@
       </c>
       <c r="W283" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X283" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -23412,10 +23885,8 @@
       <c r="L284" t="n">
         <v>4</v>
       </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M284" t="n">
+        <v>4</v>
       </c>
       <c r="N284" t="n">
         <v>1</v>
@@ -23454,6 +23925,9 @@
       </c>
       <c r="W284" t="n">
         <v>-1</v>
+      </c>
+      <c r="X284" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -23493,10 +23967,8 @@
       <c r="L285" t="n">
         <v>2</v>
       </c>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M285" t="n">
+        <v>4</v>
       </c>
       <c r="N285" t="n">
         <v>2</v>
@@ -23535,6 +24007,9 @@
       </c>
       <c r="W285" t="n">
         <v>1</v>
+      </c>
+      <c r="X285" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -23574,10 +24049,8 @@
       <c r="L286" t="n">
         <v>3</v>
       </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M286" t="n">
+        <v>5</v>
       </c>
       <c r="N286" t="n">
         <v>2</v>
@@ -23616,6 +24089,9 @@
       </c>
       <c r="W286" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X286" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -23655,10 +24131,8 @@
       <c r="L287" t="n">
         <v>2</v>
       </c>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M287" t="n">
+        <v>4</v>
       </c>
       <c r="N287" t="n">
         <v>2</v>
@@ -23697,6 +24171,9 @@
       </c>
       <c r="W287" t="n">
         <v>1</v>
+      </c>
+      <c r="X287" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -23736,10 +24213,8 @@
       <c r="L288" t="n">
         <v>3</v>
       </c>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M288" t="n">
+        <v>4</v>
       </c>
       <c r="N288" t="n">
         <v>2</v>
@@ -23778,6 +24253,9 @@
       </c>
       <c r="W288" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X288" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -23860,6 +24338,9 @@
       <c r="W289" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X289" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -23941,6 +24422,9 @@
       <c r="W290" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X290" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -23979,10 +24463,8 @@
       <c r="L291" t="n">
         <v>3</v>
       </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M291" t="n">
+        <v>4</v>
       </c>
       <c r="N291" t="n">
         <v>2</v>
@@ -24021,6 +24503,9 @@
       </c>
       <c r="W291" t="n">
         <v>1</v>
+      </c>
+      <c r="X291" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -24060,10 +24545,8 @@
       <c r="L292" t="n">
         <v>2</v>
       </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M292" t="n">
+        <v>4</v>
       </c>
       <c r="N292" t="n">
         <v>2</v>
@@ -24102,6 +24585,9 @@
       </c>
       <c r="W292" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X292" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -24141,10 +24627,8 @@
       <c r="L293" t="n">
         <v>3</v>
       </c>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M293" t="n">
+        <v>4</v>
       </c>
       <c r="N293" t="n">
         <v>2</v>
@@ -24183,6 +24667,9 @@
       </c>
       <c r="W293" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X293" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="294">
@@ -24264,6 +24751,9 @@
       </c>
       <c r="W294" t="n">
         <v>-1</v>
+      </c>
+      <c r="X294" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/split/test.xlsx
+++ b/data/split/test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X294"/>
+  <dimension ref="A1:Y294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,11 @@
           <t>men</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -616,8 +621,11 @@
       <c r="W2" t="n">
         <v>1</v>
       </c>
-      <c r="X2" t="b">
-        <v>0</v>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +706,10 @@
       <c r="W3" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X3" t="b">
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -780,8 +791,11 @@
       <c r="W4" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X4" t="b">
-        <v>0</v>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -862,8 +876,11 @@
       <c r="W5" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X5" t="b">
-        <v>0</v>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -944,8 +961,11 @@
       <c r="W6" t="n">
         <v>1</v>
       </c>
-      <c r="X6" t="b">
-        <v>0</v>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1026,8 +1046,11 @@
       <c r="W7" t="n">
         <v>-1</v>
       </c>
-      <c r="X7" t="b">
-        <v>1</v>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1108,7 +1131,10 @@
       <c r="W8" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X8" t="b">
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1190,7 +1216,10 @@
       <c r="W9" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X9" t="b">
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1272,8 +1301,11 @@
       <c r="W10" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X10" t="b">
-        <v>0</v>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1354,8 +1386,11 @@
       <c r="W11" t="n">
         <v>-1</v>
       </c>
-      <c r="X11" t="b">
-        <v>1</v>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1438,7 +1473,10 @@
       <c r="W12" t="n">
         <v>-1</v>
       </c>
-      <c r="X12" t="b">
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1522,7 +1560,10 @@
       <c r="W13" t="n">
         <v>-1</v>
       </c>
-      <c r="X13" t="b">
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1604,8 +1645,11 @@
       <c r="W14" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X14" t="b">
-        <v>0</v>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1688,7 +1732,10 @@
       <c r="W15" t="n">
         <v>-1</v>
       </c>
-      <c r="X15" t="b">
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1772,7 +1819,10 @@
       <c r="W16" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X16" t="b">
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1854,7 +1904,10 @@
       <c r="W17" t="n">
         <v>-1</v>
       </c>
-      <c r="X17" t="b">
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1938,7 +1991,10 @@
       <c r="W18" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X18" t="b">
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2022,8 +2078,11 @@
       <c r="W19" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X19" t="b">
-        <v>0</v>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2104,7 +2163,10 @@
       <c r="W20" t="n">
         <v>-1</v>
       </c>
-      <c r="X20" t="b">
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2186,8 +2248,11 @@
       <c r="W21" t="n">
         <v>-1</v>
       </c>
-      <c r="X21" t="b">
-        <v>1</v>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2270,7 +2335,10 @@
       <c r="W22" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X22" t="b">
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2352,7 +2420,10 @@
       <c r="W23" t="n">
         <v>-1</v>
       </c>
-      <c r="X23" t="b">
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2434,8 +2505,11 @@
       <c r="W24" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X24" t="b">
-        <v>0</v>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2518,8 +2592,11 @@
       <c r="W25" t="n">
         <v>-1</v>
       </c>
-      <c r="X25" t="b">
-        <v>0</v>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2600,8 +2677,11 @@
       <c r="W26" t="n">
         <v>-1</v>
       </c>
-      <c r="X26" t="b">
-        <v>0</v>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2684,7 +2764,10 @@
       <c r="W27" t="n">
         <v>-1</v>
       </c>
-      <c r="X27" t="b">
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2768,8 +2851,11 @@
       <c r="W28" t="n">
         <v>-1</v>
       </c>
-      <c r="X28" t="b">
-        <v>0</v>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2850,8 +2936,11 @@
       <c r="W29" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X29" t="b">
-        <v>0</v>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2932,7 +3021,10 @@
       <c r="W30" t="n">
         <v>-1</v>
       </c>
-      <c r="X30" t="b">
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3014,7 +3106,10 @@
       <c r="W31" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X31" t="b">
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3098,7 +3193,10 @@
       <c r="W32" t="n">
         <v>-1</v>
       </c>
-      <c r="X32" t="b">
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3182,8 +3280,11 @@
       <c r="W33" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X33" t="b">
-        <v>0</v>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3264,8 +3365,11 @@
       <c r="W34" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X34" t="b">
-        <v>0</v>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3346,7 +3450,10 @@
       <c r="W35" t="n">
         <v>-1</v>
       </c>
-      <c r="X35" t="b">
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3428,8 +3535,11 @@
       <c r="W36" t="n">
         <v>1</v>
       </c>
-      <c r="X36" t="b">
-        <v>0</v>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3512,8 +3622,11 @@
       <c r="W37" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X37" t="b">
-        <v>1</v>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3594,8 +3707,11 @@
       <c r="W38" t="n">
         <v>-1</v>
       </c>
-      <c r="X38" t="b">
-        <v>0</v>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3678,8 +3794,11 @@
       <c r="W39" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X39" t="b">
-        <v>1</v>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3762,8 +3881,11 @@
       <c r="W40" t="n">
         <v>-1</v>
       </c>
-      <c r="X40" t="b">
-        <v>1</v>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3844,7 +3966,10 @@
       <c r="W41" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X41" t="b">
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3928,7 +4053,10 @@
       <c r="W42" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X42" t="b">
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4010,7 +4138,10 @@
       <c r="W43" t="n">
         <v>1</v>
       </c>
-      <c r="X43" t="b">
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4092,8 +4223,11 @@
       <c r="W44" t="n">
         <v>-1</v>
       </c>
-      <c r="X44" t="b">
-        <v>1</v>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4174,8 +4308,11 @@
       <c r="W45" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X45" t="b">
-        <v>0</v>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4256,8 +4393,11 @@
       <c r="W46" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X46" t="b">
-        <v>1</v>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4338,8 +4478,11 @@
       <c r="W47" t="n">
         <v>-1</v>
       </c>
-      <c r="X47" t="b">
-        <v>0</v>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4420,7 +4563,10 @@
       <c r="W48" t="n">
         <v>1</v>
       </c>
-      <c r="X48" t="b">
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4504,8 +4650,11 @@
       <c r="W49" t="n">
         <v>-1</v>
       </c>
-      <c r="X49" t="b">
-        <v>1</v>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4588,7 +4737,10 @@
       <c r="W50" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X50" t="b">
+      <c r="X50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4670,7 +4822,10 @@
       <c r="W51" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X51" t="b">
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4752,8 +4907,11 @@
       <c r="W52" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X52" t="b">
-        <v>1</v>
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4836,7 +4994,10 @@
       <c r="W53" t="n">
         <v>-1</v>
       </c>
-      <c r="X53" t="b">
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4918,8 +5079,11 @@
       <c r="W54" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X54" t="b">
-        <v>1</v>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5002,8 +5166,11 @@
       <c r="W55" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X55" t="b">
-        <v>1</v>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5084,7 +5251,10 @@
       <c r="W56" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X56" t="b">
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5166,8 +5336,11 @@
       <c r="W57" t="n">
         <v>-1</v>
       </c>
-      <c r="X57" t="b">
-        <v>1</v>
+      <c r="X57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5248,8 +5421,11 @@
       <c r="W58" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X58" t="b">
-        <v>1</v>
+      <c r="X58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5330,7 +5506,10 @@
       <c r="W59" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X59" t="b">
+      <c r="X59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5414,8 +5593,11 @@
       <c r="W60" t="n">
         <v>-1</v>
       </c>
-      <c r="X60" t="b">
-        <v>0</v>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -5496,7 +5678,10 @@
       <c r="W61" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X61" t="b">
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5580,7 +5765,10 @@
       <c r="W62" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X62" t="b">
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5662,7 +5850,10 @@
       <c r="W63" t="n">
         <v>1</v>
       </c>
-      <c r="X63" t="b">
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5744,8 +5935,11 @@
       <c r="W64" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X64" t="b">
-        <v>0</v>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -5826,8 +6020,11 @@
       <c r="W65" t="n">
         <v>-1</v>
       </c>
-      <c r="X65" t="b">
-        <v>1</v>
+      <c r="X65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5910,7 +6107,10 @@
       <c r="W66" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X66" t="b">
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5992,7 +6192,10 @@
       <c r="W67" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X67" t="b">
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6074,7 +6277,10 @@
       <c r="W68" t="n">
         <v>-1</v>
       </c>
-      <c r="X68" t="b">
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6156,8 +6362,11 @@
       <c r="W69" t="n">
         <v>1</v>
       </c>
-      <c r="X69" t="b">
-        <v>1</v>
+      <c r="X69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6238,8 +6447,11 @@
       <c r="W70" t="n">
         <v>1</v>
       </c>
-      <c r="X70" t="b">
-        <v>1</v>
+      <c r="X70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6320,8 +6532,11 @@
       <c r="W71" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X71" t="b">
-        <v>0</v>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -6402,7 +6617,10 @@
       <c r="W72" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X72" t="b">
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6486,7 +6704,10 @@
       <c r="W73" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X73" t="b">
+      <c r="X73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6568,8 +6789,11 @@
       <c r="W74" t="n">
         <v>1</v>
       </c>
-      <c r="X74" t="b">
-        <v>0</v>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -6650,8 +6874,11 @@
       <c r="W75" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X75" t="b">
-        <v>1</v>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6734,7 +6961,10 @@
       <c r="W76" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X76" t="b">
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6818,8 +7048,11 @@
       <c r="W77" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X77" t="b">
-        <v>0</v>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -6900,8 +7133,11 @@
       <c r="W78" t="n">
         <v>1</v>
       </c>
-      <c r="X78" t="b">
-        <v>0</v>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6982,8 +7218,11 @@
       <c r="W79" t="n">
         <v>-1</v>
       </c>
-      <c r="X79" t="b">
-        <v>1</v>
+      <c r="X79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -7064,7 +7303,10 @@
       <c r="W80" t="n">
         <v>-1</v>
       </c>
-      <c r="X80" t="b">
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7146,8 +7388,11 @@
       <c r="W81" t="n">
         <v>-1</v>
       </c>
-      <c r="X81" t="b">
-        <v>0</v>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -7228,7 +7473,10 @@
       <c r="W82" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X82" t="b">
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7310,7 +7558,10 @@
       <c r="W83" t="n">
         <v>-1</v>
       </c>
-      <c r="X83" t="b">
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7392,7 +7643,10 @@
       <c r="W84" t="n">
         <v>-1</v>
       </c>
-      <c r="X84" t="b">
+      <c r="X84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y84" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7476,8 +7730,11 @@
       <c r="W85" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X85" t="b">
-        <v>0</v>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -7558,8 +7815,11 @@
       <c r="W86" t="n">
         <v>1</v>
       </c>
-      <c r="X86" t="b">
-        <v>0</v>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -7640,7 +7900,10 @@
       <c r="W87" t="n">
         <v>1</v>
       </c>
-      <c r="X87" t="b">
+      <c r="X87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7722,7 +7985,10 @@
       <c r="W88" t="n">
         <v>1</v>
       </c>
-      <c r="X88" t="b">
+      <c r="X88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7806,7 +8072,10 @@
       <c r="W89" t="n">
         <v>-1</v>
       </c>
-      <c r="X89" t="b">
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7888,7 +8157,10 @@
       <c r="W90" t="n">
         <v>-1</v>
       </c>
-      <c r="X90" t="b">
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7970,8 +8242,11 @@
       <c r="W91" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X91" t="b">
-        <v>0</v>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -8054,7 +8329,10 @@
       <c r="W92" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X92" t="b">
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8138,8 +8416,11 @@
       <c r="W93" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X93" t="b">
-        <v>0</v>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -8220,7 +8501,10 @@
       <c r="W94" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X94" t="b">
+      <c r="X94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8302,7 +8586,10 @@
       <c r="W95" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X95" t="b">
+      <c r="X95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y95" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8384,7 +8671,10 @@
       <c r="W96" t="n">
         <v>1</v>
       </c>
-      <c r="X96" t="b">
+      <c r="X96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y96" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8468,7 +8758,10 @@
       <c r="W97" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X97" t="b">
+      <c r="X97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8550,7 +8843,10 @@
       <c r="W98" t="n">
         <v>-1</v>
       </c>
-      <c r="X98" t="b">
+      <c r="X98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8632,7 +8928,10 @@
       <c r="W99" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X99" t="b">
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8714,7 +9013,10 @@
       <c r="W100" t="n">
         <v>-1</v>
       </c>
-      <c r="X100" t="b">
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8796,7 +9098,10 @@
       <c r="W101" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X101" t="b">
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8880,7 +9185,10 @@
       <c r="W102" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X102" t="b">
+      <c r="X102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y102" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8964,7 +9272,10 @@
       <c r="W103" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X103" t="b">
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9046,7 +9357,10 @@
       <c r="W104" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X104" t="b">
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9128,8 +9442,11 @@
       <c r="W105" t="n">
         <v>1</v>
       </c>
-      <c r="X105" t="b">
-        <v>0</v>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -9210,7 +9527,10 @@
       <c r="W106" t="n">
         <v>-1</v>
       </c>
-      <c r="X106" t="b">
+      <c r="X106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9292,7 +9612,10 @@
       <c r="W107" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X107" t="b">
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9374,8 +9697,11 @@
       <c r="W108" t="n">
         <v>-1</v>
       </c>
-      <c r="X108" t="b">
-        <v>0</v>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -9456,7 +9782,10 @@
       <c r="W109" t="n">
         <v>-1</v>
       </c>
-      <c r="X109" t="b">
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9540,8 +9869,11 @@
       <c r="W110" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X110" t="b">
-        <v>0</v>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -9622,8 +9954,11 @@
       <c r="W111" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X111" t="b">
-        <v>1</v>
+      <c r="X111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -9706,7 +10041,10 @@
       <c r="W112" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X112" t="b">
+      <c r="X112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9788,8 +10126,11 @@
       <c r="W113" t="n">
         <v>1</v>
       </c>
-      <c r="X113" t="b">
-        <v>1</v>
+      <c r="X113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -9870,8 +10211,11 @@
       <c r="W114" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X114" t="b">
-        <v>1</v>
+      <c r="X114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -9952,8 +10296,11 @@
       <c r="W115" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X115" t="b">
-        <v>0</v>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -10034,8 +10381,11 @@
       <c r="W116" t="n">
         <v>1</v>
       </c>
-      <c r="X116" t="b">
-        <v>1</v>
+      <c r="X116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -10118,8 +10468,11 @@
       <c r="W117" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X117" t="b">
-        <v>1</v>
+      <c r="X117" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -10200,7 +10553,10 @@
       <c r="W118" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X118" t="b">
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10282,7 +10638,10 @@
       <c r="W119" t="n">
         <v>1</v>
       </c>
-      <c r="X119" t="b">
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10366,8 +10725,11 @@
       <c r="W120" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X120" t="b">
-        <v>0</v>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -10448,7 +10810,10 @@
       <c r="W121" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X121" t="b">
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10530,7 +10895,10 @@
       <c r="W122" t="n">
         <v>-1</v>
       </c>
-      <c r="X122" t="b">
+      <c r="X122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10612,8 +10980,11 @@
       <c r="W123" t="n">
         <v>-1</v>
       </c>
-      <c r="X123" t="b">
-        <v>0</v>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -10696,8 +11067,11 @@
       <c r="W124" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X124" t="b">
-        <v>0</v>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -10780,7 +11154,10 @@
       <c r="W125" t="n">
         <v>-1</v>
       </c>
-      <c r="X125" t="b">
+      <c r="X125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y125" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10862,7 +11239,10 @@
       <c r="W126" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X126" t="b">
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10944,8 +11324,11 @@
       <c r="W127" t="n">
         <v>-1</v>
       </c>
-      <c r="X127" t="b">
-        <v>0</v>
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -11028,7 +11411,10 @@
       <c r="W128" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X128" t="b">
+      <c r="X128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y128" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11110,7 +11496,10 @@
       <c r="W129" t="n">
         <v>1</v>
       </c>
-      <c r="X129" t="b">
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11192,7 +11581,10 @@
       <c r="W130" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X130" t="b">
+      <c r="X130" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11276,7 +11668,10 @@
       <c r="W131" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X131" t="b">
+      <c r="X131" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y131" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11358,7 +11753,10 @@
       <c r="W132" t="n">
         <v>-1</v>
       </c>
-      <c r="X132" t="b">
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11440,7 +11838,10 @@
       <c r="W133" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X133" t="b">
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11524,8 +11925,11 @@
       <c r="W134" t="n">
         <v>1</v>
       </c>
-      <c r="X134" t="b">
-        <v>1</v>
+      <c r="X134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -11608,7 +12012,10 @@
       <c r="W135" t="n">
         <v>-1</v>
       </c>
-      <c r="X135" t="b">
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11690,7 +12097,10 @@
       <c r="W136" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X136" t="b">
+      <c r="X136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y136" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11772,8 +12182,11 @@
       <c r="W137" t="n">
         <v>1</v>
       </c>
-      <c r="X137" t="b">
-        <v>0</v>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -11854,7 +12267,10 @@
       <c r="W138" t="n">
         <v>-1</v>
       </c>
-      <c r="X138" t="b">
+      <c r="X138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11936,8 +12352,11 @@
       <c r="W139" t="n">
         <v>1</v>
       </c>
-      <c r="X139" t="b">
-        <v>0</v>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -12020,8 +12439,11 @@
       <c r="W140" t="n">
         <v>-1</v>
       </c>
-      <c r="X140" t="b">
-        <v>0</v>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -12102,7 +12524,10 @@
       <c r="W141" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X141" t="b">
+      <c r="X141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12184,7 +12609,10 @@
       <c r="W142" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X142" t="b">
+      <c r="X142" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12266,7 +12694,10 @@
       <c r="W143" t="n">
         <v>-1</v>
       </c>
-      <c r="X143" t="b">
+      <c r="X143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12350,8 +12781,11 @@
       <c r="W144" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X144" t="b">
-        <v>1</v>
+      <c r="X144" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -12434,7 +12868,10 @@
       <c r="W145" t="n">
         <v>1</v>
       </c>
-      <c r="X145" t="b">
+      <c r="X145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12518,7 +12955,10 @@
       <c r="W146" t="n">
         <v>-1</v>
       </c>
-      <c r="X146" t="b">
+      <c r="X146" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12600,7 +13040,10 @@
       <c r="W147" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X147" t="b">
+      <c r="X147" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12682,8 +13125,11 @@
       <c r="W148" t="n">
         <v>-1</v>
       </c>
-      <c r="X148" t="b">
-        <v>0</v>
+      <c r="X148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -12766,8 +13212,11 @@
       <c r="W149" t="n">
         <v>1</v>
       </c>
-      <c r="X149" t="b">
-        <v>0</v>
+      <c r="X149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -12848,8 +13297,11 @@
       <c r="W150" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X150" t="b">
-        <v>0</v>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -12930,8 +13382,11 @@
       <c r="W151" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X151" t="b">
-        <v>1</v>
+      <c r="X151" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -13014,8 +13469,11 @@
       <c r="W152" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X152" t="b">
-        <v>1</v>
+      <c r="X152" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -13098,8 +13556,11 @@
       <c r="W153" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X153" t="b">
-        <v>1</v>
+      <c r="X153" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -13180,7 +13641,10 @@
       <c r="W154" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X154" t="b">
+      <c r="X154" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y154" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13262,7 +13726,10 @@
       <c r="W155" t="n">
         <v>-1</v>
       </c>
-      <c r="X155" t="b">
+      <c r="X155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13346,8 +13813,11 @@
       <c r="W156" t="n">
         <v>-1</v>
       </c>
-      <c r="X156" t="b">
-        <v>1</v>
+      <c r="X156" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -13428,8 +13898,11 @@
       <c r="W157" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X157" t="b">
-        <v>0</v>
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -13510,8 +13983,11 @@
       <c r="W158" t="n">
         <v>-1</v>
       </c>
-      <c r="X158" t="b">
-        <v>1</v>
+      <c r="X158" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -13592,7 +14068,10 @@
       <c r="W159" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X159" t="b">
+      <c r="X159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13676,7 +14155,10 @@
       <c r="W160" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X160" t="b">
+      <c r="X160" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y160" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13760,7 +14242,10 @@
       <c r="W161" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X161" t="b">
+      <c r="X161" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y161" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13842,7 +14327,10 @@
       <c r="W162" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X162" t="b">
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13924,8 +14412,11 @@
       <c r="W163" t="n">
         <v>-1</v>
       </c>
-      <c r="X163" t="b">
-        <v>0</v>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -14006,7 +14497,10 @@
       <c r="W164" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X164" t="b">
+      <c r="X164" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y164" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14088,7 +14582,10 @@
       <c r="W165" t="n">
         <v>1</v>
       </c>
-      <c r="X165" t="b">
+      <c r="X165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14170,8 +14667,11 @@
       <c r="W166" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X166" t="b">
-        <v>1</v>
+      <c r="X166" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -14252,7 +14752,10 @@
       <c r="W167" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X167" t="b">
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14334,7 +14837,10 @@
       <c r="W168" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X168" t="b">
+      <c r="X168" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y168" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14418,8 +14924,11 @@
       <c r="W169" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X169" t="b">
-        <v>0</v>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -14500,8 +15009,11 @@
       <c r="W170" t="n">
         <v>-1</v>
       </c>
-      <c r="X170" t="b">
-        <v>0</v>
+      <c r="X170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -14582,7 +15094,10 @@
       <c r="W171" t="n">
         <v>-1</v>
       </c>
-      <c r="X171" t="b">
+      <c r="X171" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y171" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14664,7 +15179,10 @@
       <c r="W172" t="n">
         <v>-1</v>
       </c>
-      <c r="X172" t="b">
+      <c r="X172" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y172" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14748,7 +15266,10 @@
       <c r="W173" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X173" t="b">
+      <c r="X173" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y173" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14830,7 +15351,10 @@
       <c r="W174" t="n">
         <v>1</v>
       </c>
-      <c r="X174" t="b">
+      <c r="X174" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y174" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14914,7 +15438,10 @@
       <c r="W175" t="n">
         <v>-1</v>
       </c>
-      <c r="X175" t="b">
+      <c r="X175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14998,8 +15525,11 @@
       <c r="W176" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X176" t="b">
-        <v>1</v>
+      <c r="X176" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -15082,7 +15612,10 @@
       <c r="W177" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X177" t="b">
+      <c r="X177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y177" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15164,8 +15697,11 @@
       <c r="W178" t="n">
         <v>-1</v>
       </c>
-      <c r="X178" t="b">
-        <v>0</v>
+      <c r="X178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -15246,8 +15782,11 @@
       <c r="W179" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X179" t="b">
-        <v>1</v>
+      <c r="X179" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -15330,7 +15869,10 @@
       <c r="W180" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X180" t="b">
+      <c r="X180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15412,7 +15954,10 @@
       <c r="W181" t="n">
         <v>-1</v>
       </c>
-      <c r="X181" t="b">
+      <c r="X181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15494,8 +16039,11 @@
       <c r="W182" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X182" t="b">
-        <v>1</v>
+      <c r="X182" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -15576,8 +16124,11 @@
       <c r="W183" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X183" t="b">
-        <v>0</v>
+      <c r="X183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -15658,8 +16209,11 @@
       <c r="W184" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X184" t="b">
-        <v>1</v>
+      <c r="X184" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -15742,7 +16296,10 @@
       <c r="W185" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X185" t="b">
+      <c r="X185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15826,8 +16383,11 @@
       <c r="W186" t="n">
         <v>1</v>
       </c>
-      <c r="X186" t="b">
-        <v>1</v>
+      <c r="X186" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -15910,7 +16470,10 @@
       <c r="W187" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X187" t="b">
+      <c r="X187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15992,8 +16555,11 @@
       <c r="W188" t="n">
         <v>1</v>
       </c>
-      <c r="X188" t="b">
-        <v>1</v>
+      <c r="X188" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -16076,8 +16642,11 @@
       <c r="W189" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X189" t="b">
-        <v>1</v>
+      <c r="X189" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -16158,8 +16727,11 @@
       <c r="W190" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X190" t="b">
-        <v>1</v>
+      <c r="X190" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -16240,7 +16812,10 @@
       <c r="W191" t="n">
         <v>-1</v>
       </c>
-      <c r="X191" t="b">
+      <c r="X191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16322,8 +16897,11 @@
       <c r="W192" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X192" t="b">
-        <v>0</v>
+      <c r="X192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -16404,7 +16982,10 @@
       <c r="W193" t="n">
         <v>-1</v>
       </c>
-      <c r="X193" t="b">
+      <c r="X193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16488,8 +17069,11 @@
       <c r="W194" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X194" t="b">
-        <v>0</v>
+      <c r="X194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -16570,8 +17154,11 @@
       <c r="W195" t="n">
         <v>-1</v>
       </c>
-      <c r="X195" t="b">
-        <v>0</v>
+      <c r="X195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -16652,8 +17239,11 @@
       <c r="W196" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X196" t="b">
-        <v>0</v>
+      <c r="X196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -16736,8 +17326,11 @@
       <c r="W197" t="n">
         <v>-1</v>
       </c>
-      <c r="X197" t="b">
-        <v>1</v>
+      <c r="X197" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -16818,8 +17411,11 @@
       <c r="W198" t="n">
         <v>-1</v>
       </c>
-      <c r="X198" t="b">
-        <v>1</v>
+      <c r="X198" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -16902,8 +17498,11 @@
       <c r="W199" t="n">
         <v>-1</v>
       </c>
-      <c r="X199" t="b">
-        <v>1</v>
+      <c r="X199" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -16984,7 +17583,10 @@
       <c r="W200" t="n">
         <v>-1</v>
       </c>
-      <c r="X200" t="b">
+      <c r="X200" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y200" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17066,7 +17668,10 @@
       <c r="W201" t="n">
         <v>-1</v>
       </c>
-      <c r="X201" t="b">
+      <c r="X201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17148,7 +17753,10 @@
       <c r="W202" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X202" t="b">
+      <c r="X202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y202" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17230,8 +17838,11 @@
       <c r="W203" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X203" t="b">
-        <v>0</v>
+      <c r="X203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -17314,8 +17925,11 @@
       <c r="W204" t="n">
         <v>-1</v>
       </c>
-      <c r="X204" t="b">
-        <v>0</v>
+      <c r="X204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -17396,7 +18010,10 @@
       <c r="W205" t="n">
         <v>1</v>
       </c>
-      <c r="X205" t="b">
+      <c r="X205" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y205" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17480,8 +18097,11 @@
       <c r="W206" t="n">
         <v>-1</v>
       </c>
-      <c r="X206" t="b">
-        <v>0</v>
+      <c r="X206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -17562,7 +18182,10 @@
       <c r="W207" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X207" t="b">
+      <c r="X207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y207" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17646,7 +18269,10 @@
       <c r="W208" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X208" t="b">
+      <c r="X208" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y208" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17728,7 +18354,10 @@
       <c r="W209" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X209" t="b">
+      <c r="X209" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y209" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17812,7 +18441,10 @@
       <c r="W210" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X210" t="b">
+      <c r="X210" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y210" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17894,7 +18526,10 @@
       <c r="W211" t="n">
         <v>1</v>
       </c>
-      <c r="X211" t="b">
+      <c r="X211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17976,7 +18611,10 @@
       <c r="W212" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X212" t="b">
+      <c r="X212" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y212" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18058,7 +18696,10 @@
       <c r="W213" t="n">
         <v>-1</v>
       </c>
-      <c r="X213" t="b">
+      <c r="X213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y213" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18140,8 +18781,11 @@
       <c r="W214" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X214" t="b">
-        <v>1</v>
+      <c r="X214" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -18224,7 +18868,10 @@
       <c r="W215" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X215" t="b">
+      <c r="X215" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y215" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18308,8 +18955,11 @@
       <c r="W216" t="n">
         <v>-1</v>
       </c>
-      <c r="X216" t="b">
-        <v>1</v>
+      <c r="X216" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -18390,7 +19040,10 @@
       <c r="W217" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X217" t="b">
+      <c r="X217" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y217" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18474,8 +19127,11 @@
       <c r="W218" t="n">
         <v>1</v>
       </c>
-      <c r="X218" t="b">
-        <v>0</v>
+      <c r="X218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -18556,7 +19212,10 @@
       <c r="W219" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X219" t="b">
+      <c r="X219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y219" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18638,8 +19297,11 @@
       <c r="W220" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X220" t="b">
-        <v>0</v>
+      <c r="X220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -18722,7 +19384,10 @@
       <c r="W221" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X221" t="b">
+      <c r="X221" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y221" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18804,7 +19469,10 @@
       <c r="W222" t="n">
         <v>1</v>
       </c>
-      <c r="X222" t="b">
+      <c r="X222" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y222" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18888,8 +19556,11 @@
       <c r="W223" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X223" t="b">
-        <v>0</v>
+      <c r="X223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -18970,7 +19641,10 @@
       <c r="W224" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X224" t="b">
+      <c r="X224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y224" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19052,8 +19726,11 @@
       <c r="W225" t="n">
         <v>1</v>
       </c>
-      <c r="X225" t="b">
-        <v>0</v>
+      <c r="X225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -19136,7 +19813,10 @@
       <c r="W226" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X226" t="b">
+      <c r="X226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y226" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19218,7 +19898,10 @@
       <c r="W227" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X227" t="b">
+      <c r="X227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19300,8 +19983,11 @@
       <c r="W228" t="n">
         <v>-1</v>
       </c>
-      <c r="X228" t="b">
-        <v>0</v>
+      <c r="X228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -19382,8 +20068,11 @@
       <c r="W229" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X229" t="b">
-        <v>1</v>
+      <c r="X229" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -19466,7 +20155,10 @@
       <c r="W230" t="n">
         <v>-1</v>
       </c>
-      <c r="X230" t="b">
+      <c r="X230" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y230" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19550,8 +20242,11 @@
       <c r="W231" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X231" t="b">
-        <v>1</v>
+      <c r="X231" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -19634,8 +20329,11 @@
       <c r="W232" t="n">
         <v>1</v>
       </c>
-      <c r="X232" t="b">
-        <v>0</v>
+      <c r="X232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -19716,8 +20414,11 @@
       <c r="W233" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X233" t="b">
-        <v>1</v>
+      <c r="X233" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -19800,8 +20501,11 @@
       <c r="W234" t="n">
         <v>-1</v>
       </c>
-      <c r="X234" t="b">
-        <v>1</v>
+      <c r="X234" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -19884,8 +20588,11 @@
       <c r="W235" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X235" t="b">
-        <v>1</v>
+      <c r="X235" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -19968,8 +20675,11 @@
       <c r="W236" t="n">
         <v>-1</v>
       </c>
-      <c r="X236" t="b">
-        <v>0</v>
+      <c r="X236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -20052,7 +20762,10 @@
       <c r="W237" t="n">
         <v>-1</v>
       </c>
-      <c r="X237" t="b">
+      <c r="X237" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y237" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20134,7 +20847,10 @@
       <c r="W238" t="n">
         <v>-1</v>
       </c>
-      <c r="X238" t="b">
+      <c r="X238" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y238" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20216,7 +20932,10 @@
       <c r="W239" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X239" t="b">
+      <c r="X239" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y239" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20300,7 +21019,10 @@
       <c r="W240" t="n">
         <v>-1</v>
       </c>
-      <c r="X240" t="b">
+      <c r="X240" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y240" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20382,8 +21104,11 @@
       <c r="W241" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X241" t="b">
-        <v>0</v>
+      <c r="X241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -20464,7 +21189,10 @@
       <c r="W242" t="n">
         <v>-1</v>
       </c>
-      <c r="X242" t="b">
+      <c r="X242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y242" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20546,7 +21274,10 @@
       <c r="W243" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X243" t="b">
+      <c r="X243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y243" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20628,8 +21359,11 @@
       <c r="W244" t="n">
         <v>-1</v>
       </c>
-      <c r="X244" t="b">
-        <v>1</v>
+      <c r="X244" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -20712,7 +21446,10 @@
       <c r="W245" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X245" t="b">
+      <c r="X245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y245" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20794,8 +21531,11 @@
       <c r="W246" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X246" t="b">
-        <v>0</v>
+      <c r="X246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -20876,7 +21616,10 @@
       <c r="W247" t="n">
         <v>1</v>
       </c>
-      <c r="X247" t="b">
+      <c r="X247" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y247" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20958,7 +21701,10 @@
       <c r="W248" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X248" t="b">
+      <c r="X248" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y248" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21042,7 +21788,10 @@
       <c r="W249" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X249" t="b">
+      <c r="X249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y249" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21126,7 +21875,10 @@
       <c r="W250" t="n">
         <v>-1</v>
       </c>
-      <c r="X250" t="b">
+      <c r="X250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y250" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21208,7 +21960,10 @@
       <c r="W251" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X251" t="b">
+      <c r="X251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y251" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21290,7 +22045,10 @@
       <c r="W252" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X252" t="b">
+      <c r="X252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21372,7 +22130,10 @@
       <c r="W253" t="n">
         <v>-1</v>
       </c>
-      <c r="X253" t="b">
+      <c r="X253" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y253" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21456,8 +22217,11 @@
       <c r="W254" t="n">
         <v>1</v>
       </c>
-      <c r="X254" t="b">
-        <v>0</v>
+      <c r="X254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -21540,8 +22304,11 @@
       <c r="W255" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X255" t="b">
-        <v>0</v>
+      <c r="X255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -21624,7 +22391,10 @@
       <c r="W256" t="n">
         <v>-1</v>
       </c>
-      <c r="X256" t="b">
+      <c r="X256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y256" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21706,8 +22476,11 @@
       <c r="W257" t="n">
         <v>-1</v>
       </c>
-      <c r="X257" t="b">
-        <v>1</v>
+      <c r="X257" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -21788,7 +22561,10 @@
       <c r="W258" t="n">
         <v>-1</v>
       </c>
-      <c r="X258" t="b">
+      <c r="X258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y258" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21870,7 +22646,10 @@
       <c r="W259" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X259" t="b">
+      <c r="X259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y259" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21952,7 +22731,10 @@
       <c r="W260" t="n">
         <v>1</v>
       </c>
-      <c r="X260" t="b">
+      <c r="X260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y260" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22034,8 +22816,11 @@
       <c r="W261" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X261" t="b">
-        <v>1</v>
+      <c r="X261" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -22116,8 +22901,11 @@
       <c r="W262" t="n">
         <v>-1</v>
       </c>
-      <c r="X262" t="b">
-        <v>1</v>
+      <c r="X262" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -22198,7 +22986,10 @@
       <c r="W263" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X263" t="b">
+      <c r="X263" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y263" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22280,8 +23071,11 @@
       <c r="W264" t="n">
         <v>-1</v>
       </c>
-      <c r="X264" t="b">
-        <v>0</v>
+      <c r="X264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -22364,7 +23158,10 @@
       <c r="W265" t="n">
         <v>-1</v>
       </c>
-      <c r="X265" t="b">
+      <c r="X265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y265" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22446,8 +23243,11 @@
       <c r="W266" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X266" t="b">
-        <v>0</v>
+      <c r="X266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -22528,8 +23328,11 @@
       <c r="W267" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X267" t="b">
-        <v>0</v>
+      <c r="X267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -22610,7 +23413,10 @@
       <c r="W268" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X268" t="b">
+      <c r="X268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y268" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22692,8 +23498,11 @@
       <c r="W269" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X269" t="b">
-        <v>0</v>
+      <c r="X269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -22776,7 +23585,10 @@
       <c r="W270" t="n">
         <v>-1</v>
       </c>
-      <c r="X270" t="b">
+      <c r="X270" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y270" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22858,7 +23670,10 @@
       <c r="W271" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X271" t="b">
+      <c r="X271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y271" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22940,8 +23755,11 @@
       <c r="W272" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X272" t="b">
-        <v>0</v>
+      <c r="X272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -23022,7 +23840,10 @@
       <c r="W273" t="n">
         <v>-1</v>
       </c>
-      <c r="X273" t="b">
+      <c r="X273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y273" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23106,8 +23927,11 @@
       <c r="W274" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X274" t="b">
-        <v>1</v>
+      <c r="X274" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -23188,7 +24012,10 @@
       <c r="W275" t="n">
         <v>-1</v>
       </c>
-      <c r="X275" t="b">
+      <c r="X275" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y275" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23270,8 +24097,11 @@
       <c r="W276" t="n">
         <v>-1</v>
       </c>
-      <c r="X276" t="b">
-        <v>0</v>
+      <c r="X276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -23352,8 +24182,11 @@
       <c r="W277" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X277" t="b">
-        <v>0</v>
+      <c r="X277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -23434,8 +24267,11 @@
       <c r="W278" t="n">
         <v>1</v>
       </c>
-      <c r="X278" t="b">
-        <v>1</v>
+      <c r="X278" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -23516,7 +24352,10 @@
       <c r="W279" t="n">
         <v>-1</v>
       </c>
-      <c r="X279" t="b">
+      <c r="X279" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y279" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23598,7 +24437,10 @@
       <c r="W280" t="n">
         <v>1</v>
       </c>
-      <c r="X280" t="b">
+      <c r="X280" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y280" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23680,7 +24522,10 @@
       <c r="W281" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X281" t="b">
+      <c r="X281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y281" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23762,8 +24607,11 @@
       <c r="W282" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X282" t="b">
-        <v>1</v>
+      <c r="X282" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -23844,8 +24692,11 @@
       <c r="W283" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X283" t="b">
-        <v>0</v>
+      <c r="X283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -23926,8 +24777,11 @@
       <c r="W284" t="n">
         <v>-1</v>
       </c>
-      <c r="X284" t="b">
-        <v>0</v>
+      <c r="X284" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -24008,8 +24862,11 @@
       <c r="W285" t="n">
         <v>1</v>
       </c>
-      <c r="X285" t="b">
-        <v>0</v>
+      <c r="X285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="286">
@@ -24090,8 +24947,11 @@
       <c r="W286" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X286" t="b">
-        <v>0</v>
+      <c r="X286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -24172,8 +25032,11 @@
       <c r="W287" t="n">
         <v>1</v>
       </c>
-      <c r="X287" t="b">
-        <v>0</v>
+      <c r="X287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -24254,8 +25117,11 @@
       <c r="W288" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X288" t="b">
-        <v>0</v>
+      <c r="X288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -24338,8 +25204,11 @@
       <c r="W289" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X289" t="b">
-        <v>0</v>
+      <c r="X289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -24422,7 +25291,10 @@
       <c r="W290" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X290" t="b">
+      <c r="X290" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y290" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24504,8 +25376,11 @@
       <c r="W291" t="n">
         <v>1</v>
       </c>
-      <c r="X291" t="b">
-        <v>0</v>
+      <c r="X291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -24586,7 +25461,10 @@
       <c r="W292" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X292" t="b">
+      <c r="X292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y292" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24668,8 +25546,11 @@
       <c r="W293" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X293" t="b">
-        <v>1</v>
+      <c r="X293" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -24752,8 +25633,11 @@
       <c r="W294" t="n">
         <v>-1</v>
       </c>
-      <c r="X294" t="b">
-        <v>0</v>
+      <c r="X294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
